--- a/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
+++ b/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
@@ -1657,7 +1657,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>総合事業費　令和7年度の総合事業の実績</t>
+          <t>総合事業費　令和7年度の総合事業の事業費</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>総合事業の量の見込み　同上</t>
+          <t>総合事業の量の見込み　事業ごとの利用者実人数（令和7年度）</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">

--- a/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
+++ b/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
@@ -19,6 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_給付費と保険料" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_暫定値である理由" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_自己点検" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_令和8年9月18日版との対照" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -136,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -222,6 +223,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -588,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1108,16 +1112,41 @@
       <c r="H26" s="6" t="inlineStr"/>
       <c r="I26" s="6" t="inlineStr"/>
     </row>
-    <row r="27"/>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>12_令和8年9月18日版との対照</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>先にお示しした版から動いたもの・動かないもの</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr"/>
+      <c r="I27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28"/>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>3　当方の29区分と見える化の45区分は束ね方が違います</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="74" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30" ht="74" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>当方の区分は見える化システムの総括表詳細（１）の29区分です。見える化の入力画面は45区分（介護28・介護予防17）ですが、その区分一覧そのものは受領していません（件数のみ弊社内の全国共通版により把握しています）。
 介護予防支援・居宅介護支援のように、総括表では1行、入力画面では2区分になるものがあります。このため03・04シートは要支援の列と要介護の列を分けて掲げ、どちらの区分にも貼れる形にしています。
@@ -1130,11 +1159,11 @@
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="A29:I29"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A28:I28"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A6:I6"/>
     <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A30:I30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
@@ -2512,7 +2541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2988,27 +3017,52 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="9" t="inlineStr"/>
-      <c r="B22" s="9" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>書き出した表の内訳の和と「計」の欄が一致すること</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>02・03・04・05シートの全行を読み直して検算</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>378行を検算／合わない なし</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="9" t="inlineStr"/>
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>自己点検の結果</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr"/>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>適合17件・不適合0件</t>
-        </is>
-      </c>
-      <c r="E22" s="26" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr"/>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>適合18件・不適合0件</t>
+        </is>
+      </c>
+      <c r="E23" s="26" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>注）本シートは点検の記録であり、本表の値が暫定値であることを変えるものではありません。点検しているのは内的整合であって、未受領の資料により値が動くことは点検では解消しません。</t>
         </is>
@@ -3018,7 +3072,628 @@
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A24:E24"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"游ゴシック"&amp;8 本表の値は必要資料が未受領であることによる暫定値です。確定値ではありません。（基準日 令和8年9月18日）</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>令和8年9月18日にお示しした版との対照</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>本表の値は必要資料が未受領であることによる暫定値です。確定値ではありません。　先にお示しした令和8年9月18日版から、動いたものと動かなかったものを示します。令和7年度の給付費データの差（確認事項No.87）が解消したことにより見込量を直す必要があるかどうかを含め、9月18日版と現在の算定を年度ごとに突き合わせて確かめた結果です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>1　動かなかったもの（見込量・給付費・保険料）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="5" t="inlineStr"/>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>9月18日版</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>現在の算定</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>要介護度別の認定者数</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>令和9〜11・17・22年度</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>同じ</t>
+        </is>
+      </c>
+      <c r="E6" s="30" t="inlineStr">
+        <is>
+          <t>変わらない</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>施設・居住系サービス利用者数（8区分）</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>同じ</t>
+        </is>
+      </c>
+      <c r="E7" s="30" t="inlineStr">
+        <is>
+          <t>変わらない</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>在宅サービス利用者数（21区分）</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>同じ</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="inlineStr">
+        <is>
+          <t>変わらない</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>在宅サービス利用回（日）数（12区分）</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>同じ</t>
+        </is>
+      </c>
+      <c r="E9" s="30" t="inlineStr">
+        <is>
+          <t>変わらない</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業の見込み量</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度の利用者実人数を据え置き</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>同じ（据え置きのまま）</t>
+        </is>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
+        <is>
+          <t>変わらない</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>総給付費（第10期3か年計）</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>9,031,900,444円</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>9,031,900,444円</t>
+        </is>
+      </c>
+      <c r="E11" s="30" t="inlineStr">
+        <is>
+          <t>変わらない</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>算定上の月額基準額</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>6,436円</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>6,436円</t>
+        </is>
+      </c>
+      <c r="E12" s="30" t="inlineStr">
+        <is>
+          <t>変わらない</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>保険料基準額（百円未満四捨五入）</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>6,400円</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>6,400円</t>
+        </is>
+      </c>
+      <c r="E13" s="30" t="inlineStr">
+        <is>
+          <t>変わらない</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>注1）上の5年度について、要介護度別の値を1行ずつ突き合わせています（認定者数・施設居住系・在宅・回（日）数の計252行）。
+注2）本表の値は必要資料が未受領であることによる暫定値です。確定値ではありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>2　給付費データの差が解消したこと（確認事項No.87）の影響</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="5" t="inlineStr"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>みるところ</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>見込量への影響</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>解消した差の内容</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>令和7年度の給付費データについて、表（介護度別給付費）の総計と同じファイルの明細の集計に129,580,267円の差があった。再提供を受けたファイルで解消し、要支援1から要介護5までの全7区分で3町合計と円単位で一致した。</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>見込量（利用者数・回（日）数）が使う資料</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>介護保険事業状況報告（年報）の要介護度別の明細と、将来推計の年齢階級別人口。給付費データは用いていない。</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>影響しない</t>
+        </is>
+      </c>
+      <c r="E19" s="30" t="inlineStr">
+        <is>
+          <t>直す必要がない</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>給付費が使う資料</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの総括表詳細（４）の1人1月あたり給付費。基準年度の給付費2,915,307,125円は総括表と円単位で一致している。</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>影響しない</t>
+        </is>
+      </c>
+      <c r="E20" s="30" t="inlineStr">
+        <is>
+          <t>直す必要がない</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>給付費データを使っている唯一の箇所</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>要介護度間の単価の比（形）だけを採っている。解消したのは介護度別給付費の表の値であり、比を採っている1人1月あたり給付費・月平均利用者数の表は変わっていない。加えて、比は年報の利用者数で加重した平均が総括表の単価と一致するよう比例調整するため、総額は総括表に固定される。</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>影響しない</t>
+        </is>
+      </c>
+      <c r="E21" s="30" t="inlineStr">
+        <is>
+          <t>直す必要がない</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>差が解消したことで変わったところ</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度の単価の残差が、分母が一つに定まったことにより＋1.63％から＋5.90％の幅ではなく＋1.63％の単一の値になった。これは単価を令和7年度で固定していることの大きさ（据え置き項目）の示し方であり、本表の見込量には入れていない。</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>本表の値は動かない</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>据え置きの説明を改めた</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>3　動いたもの（加えたもの）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="5" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>加えたもの</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>9月18日版</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>現在</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>掲げる年度</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>令和9・10・11・17・22年度の5年度</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>令和9年度／令和10年度／令和11年度／令和12年度／令和17年度／令和22年度／令和27年度／令和32年度</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムが求める年度に合わせて広げました（確認事項No.157）。計画本文に掲げるのは令和17・22年度のままです</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>所得段階別第1号被保険者数</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>08シートに16段階×8年度</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムが所得段階別の入力を求めるためです（確認事項No.156）。当連合の所得段階は第9期の条例により16段階です</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>本シート</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>12シート</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>9月18日版との対照を残すためです</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>注）年度を広げたことにより、令和12年度に地域密着型介護老人福祉施設入所者生活介護が定員62人に達する見込みであることが分かりました。9月18日版では令和11年度の次に算定していたのが令和17年度であったため、定員に達するのは令和17年度と読んでいました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>4　お手元の9月18日版との1か所の食い違い</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="5" t="inlineStr"/>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>箇所</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>お手元の版</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>当方の9月18日版・現在</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>扱い</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>05_利用回日数　認知症対応型通所介護　令和10年度　計</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>内訳（要介護2 8.2）と合わないため8.2が正しい</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>注）ほかの全ての欄はお手元の版と当方の9月18日版で一致しています。本表では内訳と計が全ての行で一致することを自己点検で確かめています。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>

--- a/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
+++ b/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -222,6 +222,21 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3165,7 +3180,7 @@
           <t>同じ</t>
         </is>
       </c>
-      <c r="E6" s="30" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>変わらない</t>
         </is>
@@ -3190,7 +3205,7 @@
           <t>同じ</t>
         </is>
       </c>
-      <c r="E7" s="30" t="inlineStr">
+      <c r="E7" s="35" t="inlineStr">
         <is>
           <t>変わらない</t>
         </is>
@@ -3215,7 +3230,7 @@
           <t>同じ</t>
         </is>
       </c>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="E8" s="35" t="inlineStr">
         <is>
           <t>変わらない</t>
         </is>
@@ -3240,7 +3255,7 @@
           <t>同じ</t>
         </is>
       </c>
-      <c r="E9" s="30" t="inlineStr">
+      <c r="E9" s="35" t="inlineStr">
         <is>
           <t>変わらない</t>
         </is>
@@ -3265,7 +3280,7 @@
           <t>同じ（据え置きのまま）</t>
         </is>
       </c>
-      <c r="E10" s="30" t="inlineStr">
+      <c r="E10" s="35" t="inlineStr">
         <is>
           <t>変わらない</t>
         </is>
@@ -3290,7 +3305,7 @@
           <t>9,031,900,444円</t>
         </is>
       </c>
-      <c r="E11" s="30" t="inlineStr">
+      <c r="E11" s="35" t="inlineStr">
         <is>
           <t>変わらない</t>
         </is>
@@ -3315,7 +3330,7 @@
           <t>6,436円</t>
         </is>
       </c>
-      <c r="E12" s="30" t="inlineStr">
+      <c r="E12" s="35" t="inlineStr">
         <is>
           <t>変わらない</t>
         </is>
@@ -3340,7 +3355,7 @@
           <t>6,400円</t>
         </is>
       </c>
-      <c r="E13" s="30" t="inlineStr">
+      <c r="E13" s="35" t="inlineStr">
         <is>
           <t>変わらない</t>
         </is>
@@ -3428,7 +3443,7 @@
           <t>影響しない</t>
         </is>
       </c>
-      <c r="E19" s="30" t="inlineStr">
+      <c r="E19" s="35" t="inlineStr">
         <is>
           <t>直す必要がない</t>
         </is>
@@ -3453,7 +3468,7 @@
           <t>影響しない</t>
         </is>
       </c>
-      <c r="E20" s="30" t="inlineStr">
+      <c r="E20" s="35" t="inlineStr">
         <is>
           <t>直す必要がない</t>
         </is>
@@ -3478,7 +3493,7 @@
           <t>影響しない</t>
         </is>
       </c>
-      <c r="E21" s="30" t="inlineStr">
+      <c r="E21" s="35" t="inlineStr">
         <is>
           <t>直す必要がない</t>
         </is>
@@ -19956,7 +19971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -20785,11 +20800,1150 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>2　「①標準段階区分・割合」の画面に入れる場合（13段階へ束ねる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>段階</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>画面の割合</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>基準所得金額</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>第1段階</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="D28" s="21" t="n">
+        <v>1462</v>
+      </c>
+      <c r="E28" s="21" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F28" s="21" t="n">
+        <v>1473</v>
+      </c>
+      <c r="G28" s="21" t="n">
+        <v>1473</v>
+      </c>
+      <c r="H28" s="21" t="n">
+        <v>1479</v>
+      </c>
+      <c r="I28" s="21" t="n">
+        <v>1517</v>
+      </c>
+      <c r="J28" s="21" t="n">
+        <v>1502</v>
+      </c>
+      <c r="K28" s="21" t="n">
+        <v>1459</v>
+      </c>
+      <c r="L28" s="22" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>第2段階</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="D29" s="21" t="n">
+        <v>1178</v>
+      </c>
+      <c r="E29" s="21" t="n">
+        <v>1182</v>
+      </c>
+      <c r="F29" s="21" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G29" s="21" t="n">
+        <v>1186</v>
+      </c>
+      <c r="H29" s="21" t="n">
+        <v>1191</v>
+      </c>
+      <c r="I29" s="21" t="n">
+        <v>1222</v>
+      </c>
+      <c r="J29" s="21" t="n">
+        <v>1209</v>
+      </c>
+      <c r="K29" s="21" t="n">
+        <v>1175</v>
+      </c>
+      <c r="L29" s="22" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>第3段階</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D30" s="21" t="n">
+        <v>937</v>
+      </c>
+      <c r="E30" s="21" t="n">
+        <v>940</v>
+      </c>
+      <c r="F30" s="21" t="n">
+        <v>944</v>
+      </c>
+      <c r="G30" s="21" t="n">
+        <v>943</v>
+      </c>
+      <c r="H30" s="21" t="n">
+        <v>947</v>
+      </c>
+      <c r="I30" s="21" t="n">
+        <v>972</v>
+      </c>
+      <c r="J30" s="21" t="n">
+        <v>962</v>
+      </c>
+      <c r="K30" s="21" t="n">
+        <v>935</v>
+      </c>
+      <c r="L30" s="22" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>第4段階</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D31" s="21" t="n">
+        <v>753</v>
+      </c>
+      <c r="E31" s="21" t="n">
+        <v>756</v>
+      </c>
+      <c r="F31" s="21" t="n">
+        <v>759</v>
+      </c>
+      <c r="G31" s="21" t="n">
+        <v>758</v>
+      </c>
+      <c r="H31" s="21" t="n">
+        <v>762</v>
+      </c>
+      <c r="I31" s="21" t="n">
+        <v>782</v>
+      </c>
+      <c r="J31" s="21" t="n">
+        <v>773</v>
+      </c>
+      <c r="K31" s="21" t="n">
+        <v>751</v>
+      </c>
+      <c r="L31" s="22" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>第5段階</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="21" t="n">
+        <v>1185</v>
+      </c>
+      <c r="E32" s="21" t="n">
+        <v>1189</v>
+      </c>
+      <c r="F32" s="21" t="n">
+        <v>1193</v>
+      </c>
+      <c r="G32" s="21" t="n">
+        <v>1193</v>
+      </c>
+      <c r="H32" s="21" t="n">
+        <v>1198</v>
+      </c>
+      <c r="I32" s="21" t="n">
+        <v>1229</v>
+      </c>
+      <c r="J32" s="21" t="n">
+        <v>1217</v>
+      </c>
+      <c r="K32" s="21" t="n">
+        <v>1182</v>
+      </c>
+      <c r="L32" s="22" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>第6段階</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D33" s="21" t="n">
+        <v>1382</v>
+      </c>
+      <c r="E33" s="21" t="n">
+        <v>1387</v>
+      </c>
+      <c r="F33" s="21" t="n">
+        <v>1392</v>
+      </c>
+      <c r="G33" s="21" t="n">
+        <v>1392</v>
+      </c>
+      <c r="H33" s="21" t="n">
+        <v>1398</v>
+      </c>
+      <c r="I33" s="21" t="n">
+        <v>1434</v>
+      </c>
+      <c r="J33" s="21" t="n">
+        <v>1420</v>
+      </c>
+      <c r="K33" s="21" t="n">
+        <v>1379</v>
+      </c>
+      <c r="L33" s="22" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>第7段階</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D34" s="21" t="n">
+        <v>1233</v>
+      </c>
+      <c r="E34" s="21" t="n">
+        <v>1238</v>
+      </c>
+      <c r="F34" s="21" t="n">
+        <v>1242</v>
+      </c>
+      <c r="G34" s="21" t="n">
+        <v>1242</v>
+      </c>
+      <c r="H34" s="21" t="n">
+        <v>1247</v>
+      </c>
+      <c r="I34" s="21" t="n">
+        <v>1280</v>
+      </c>
+      <c r="J34" s="21" t="n">
+        <v>1267</v>
+      </c>
+      <c r="K34" s="21" t="n">
+        <v>1231</v>
+      </c>
+      <c r="L34" s="22" t="n">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>第8段階</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D35" s="21" t="n">
+        <v>527</v>
+      </c>
+      <c r="E35" s="21" t="n">
+        <v>529</v>
+      </c>
+      <c r="F35" s="21" t="n">
+        <v>531</v>
+      </c>
+      <c r="G35" s="21" t="n">
+        <v>531</v>
+      </c>
+      <c r="H35" s="21" t="n">
+        <v>533</v>
+      </c>
+      <c r="I35" s="21" t="n">
+        <v>547</v>
+      </c>
+      <c r="J35" s="21" t="n">
+        <v>542</v>
+      </c>
+      <c r="K35" s="21" t="n">
+        <v>526</v>
+      </c>
+      <c r="L35" s="22" t="n">
+        <v>2100000</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>第9段階</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D36" s="21" t="n">
+        <v>203</v>
+      </c>
+      <c r="E36" s="21" t="n">
+        <v>204</v>
+      </c>
+      <c r="F36" s="21" t="n">
+        <v>204</v>
+      </c>
+      <c r="G36" s="21" t="n">
+        <v>204</v>
+      </c>
+      <c r="H36" s="21" t="n">
+        <v>205</v>
+      </c>
+      <c r="I36" s="21" t="n">
+        <v>210</v>
+      </c>
+      <c r="J36" s="21" t="n">
+        <v>208</v>
+      </c>
+      <c r="K36" s="21" t="n">
+        <v>202</v>
+      </c>
+      <c r="L36" s="22" t="n">
+        <v>3200000</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>第10段階</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D37" s="21" t="n">
+        <v>100</v>
+      </c>
+      <c r="E37" s="21" t="n">
+        <v>100</v>
+      </c>
+      <c r="F37" s="21" t="n">
+        <v>101</v>
+      </c>
+      <c r="G37" s="21" t="n">
+        <v>101</v>
+      </c>
+      <c r="H37" s="21" t="n">
+        <v>101</v>
+      </c>
+      <c r="I37" s="21" t="n">
+        <v>104</v>
+      </c>
+      <c r="J37" s="21" t="n">
+        <v>103</v>
+      </c>
+      <c r="K37" s="21" t="n">
+        <v>100</v>
+      </c>
+      <c r="L37" s="22" t="n">
+        <v>4200000</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>第11段階</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D38" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="E38" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="F38" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="G38" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="H38" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="I38" s="21" t="n">
+        <v>56</v>
+      </c>
+      <c r="J38" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="K38" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="L38" s="22" t="n">
+        <v>5200000</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>第12段階</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D39" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="E39" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="F39" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="G39" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="H39" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="I39" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="J39" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="K39" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="L39" s="22" t="n">
+        <v>6200000</v>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>第13段階</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D40" s="21" t="n">
+        <v>109</v>
+      </c>
+      <c r="E40" s="21" t="n">
+        <v>109</v>
+      </c>
+      <c r="F40" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="G40" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="H40" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="I40" s="21" t="n">
+        <v>113</v>
+      </c>
+      <c r="J40" s="21" t="n">
+        <v>112</v>
+      </c>
+      <c r="K40" s="21" t="n">
+        <v>109</v>
+      </c>
+      <c r="L40" s="22" t="n">
+        <v>7200000</v>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="23" t="inlineStr"/>
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D41" s="25" t="n">
+        <v>9147</v>
+      </c>
+      <c r="E41" s="25" t="n">
+        <v>9179</v>
+      </c>
+      <c r="F41" s="25" t="n">
+        <v>9213</v>
+      </c>
+      <c r="G41" s="25" t="n">
+        <v>9211</v>
+      </c>
+      <c r="H41" s="25" t="n">
+        <v>9250</v>
+      </c>
+      <c r="I41" s="25" t="n">
+        <v>9491</v>
+      </c>
+      <c r="J41" s="25" t="n">
+        <v>9395</v>
+      </c>
+      <c r="K41" s="25" t="n">
+        <v>9127</v>
+      </c>
+      <c r="L41" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="13" t="inlineStr"/>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>補正後被保険者数</t>
+        </is>
+      </c>
+      <c r="C42" s="30" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D42" s="31" t="n">
+        <v>8998.5</v>
+      </c>
+      <c r="E42" s="31" t="n">
+        <v>9029.5</v>
+      </c>
+      <c r="F42" s="31" t="n">
+        <v>9062.9</v>
+      </c>
+      <c r="G42" s="31" t="n">
+        <v>9061.299999999999</v>
+      </c>
+      <c r="H42" s="31" t="n">
+        <v>9099.299999999999</v>
+      </c>
+      <c r="I42" s="31" t="n">
+        <v>9337</v>
+      </c>
+      <c r="J42" s="31" t="n">
+        <v>9243.299999999999</v>
+      </c>
+      <c r="K42" s="31" t="n">
+        <v>8979.5</v>
+      </c>
+      <c r="L42" s="32" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="118" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>注1）本表の値は必要資料が未受領であることによる暫定値です。確定値ではありません。
+注2）画面に表示されている割合は国の標準（13段階）であり、当連合の条例の乗率とは異なります。第2・第4・第6から第9・第11から第13段階の9つで違いがあり、第14から第16段階（多段階化した分）は標準にありません。本表の人数を標準の割合のまま入れると、第10期3か年の補正後被保険者数は27,090.8人（条例の乗率なら27,298.8人）となり、算定上の月額は6436円から6485円へ+49円動きます。
+注3）したがって、所得段階の設定は「弾力化」を選び、1の表（16段階）の人数と乗率を入れることを基本とします。標準の13段階のまま入れるのは、画面が弾力化を受け付けない場合に限ります。
+注4）画面が表示する第1号被保険者数は人口の設定によります。人口の設定が社人研のままのとき、画面は令和9年度9,116人・令和10年度9,110人・令和11年度9,107人を表示します。本表の計（9,147人・9,179人・9,213人）は案Cによるものであり、先に人口の設定を案Cに改めないと計が画面と合いません（確認事項No.127）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>3　人口の設定を改めない場合（計を画面の第1号被保険者数に合わせる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="5" t="inlineStr"/>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>段階</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>画面の割合</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="inlineStr"/>
+      <c r="L46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>第1段階</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="D47" s="21" t="n">
+        <v>1457</v>
+      </c>
+      <c r="E47" s="21" t="n">
+        <v>1456</v>
+      </c>
+      <c r="F47" s="21" t="n">
+        <v>1456</v>
+      </c>
+      <c r="G47" s="33" t="inlineStr"/>
+      <c r="H47" s="33" t="inlineStr"/>
+      <c r="I47" s="33" t="inlineStr"/>
+      <c r="J47" s="33" t="inlineStr"/>
+      <c r="K47" s="33" t="inlineStr"/>
+      <c r="L47" s="33" t="inlineStr"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>第2段階</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="D48" s="21" t="n">
+        <v>1174</v>
+      </c>
+      <c r="E48" s="21" t="n">
+        <v>1173</v>
+      </c>
+      <c r="F48" s="21" t="n">
+        <v>1172</v>
+      </c>
+      <c r="G48" s="33" t="inlineStr"/>
+      <c r="H48" s="33" t="inlineStr"/>
+      <c r="I48" s="33" t="inlineStr"/>
+      <c r="J48" s="33" t="inlineStr"/>
+      <c r="K48" s="33" t="inlineStr"/>
+      <c r="L48" s="33" t="inlineStr"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>第3段階</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D49" s="21" t="n">
+        <v>934</v>
+      </c>
+      <c r="E49" s="21" t="n">
+        <v>933</v>
+      </c>
+      <c r="F49" s="21" t="n">
+        <v>933</v>
+      </c>
+      <c r="G49" s="33" t="inlineStr"/>
+      <c r="H49" s="33" t="inlineStr"/>
+      <c r="I49" s="33" t="inlineStr"/>
+      <c r="J49" s="33" t="inlineStr"/>
+      <c r="K49" s="33" t="inlineStr"/>
+      <c r="L49" s="33" t="inlineStr"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>第4段階</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D50" s="21" t="n">
+        <v>750</v>
+      </c>
+      <c r="E50" s="21" t="n">
+        <v>750</v>
+      </c>
+      <c r="F50" s="21" t="n">
+        <v>750</v>
+      </c>
+      <c r="G50" s="33" t="inlineStr"/>
+      <c r="H50" s="33" t="inlineStr"/>
+      <c r="I50" s="33" t="inlineStr"/>
+      <c r="J50" s="33" t="inlineStr"/>
+      <c r="K50" s="33" t="inlineStr"/>
+      <c r="L50" s="33" t="inlineStr"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>第5段階</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="21" t="n">
+        <v>1181</v>
+      </c>
+      <c r="E51" s="21" t="n">
+        <v>1180</v>
+      </c>
+      <c r="F51" s="21" t="n">
+        <v>1179</v>
+      </c>
+      <c r="G51" s="33" t="inlineStr"/>
+      <c r="H51" s="33" t="inlineStr"/>
+      <c r="I51" s="33" t="inlineStr"/>
+      <c r="J51" s="33" t="inlineStr"/>
+      <c r="K51" s="33" t="inlineStr"/>
+      <c r="L51" s="33" t="inlineStr"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>第6段階</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D52" s="21" t="n">
+        <v>1378</v>
+      </c>
+      <c r="E52" s="21" t="n">
+        <v>1377</v>
+      </c>
+      <c r="F52" s="21" t="n">
+        <v>1376</v>
+      </c>
+      <c r="G52" s="33" t="inlineStr"/>
+      <c r="H52" s="33" t="inlineStr"/>
+      <c r="I52" s="33" t="inlineStr"/>
+      <c r="J52" s="33" t="inlineStr"/>
+      <c r="K52" s="33" t="inlineStr"/>
+      <c r="L52" s="33" t="inlineStr"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>第7段階</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D53" s="21" t="n">
+        <v>1229</v>
+      </c>
+      <c r="E53" s="21" t="n">
+        <v>1229</v>
+      </c>
+      <c r="F53" s="21" t="n">
+        <v>1228</v>
+      </c>
+      <c r="G53" s="33" t="inlineStr"/>
+      <c r="H53" s="33" t="inlineStr"/>
+      <c r="I53" s="33" t="inlineStr"/>
+      <c r="J53" s="33" t="inlineStr"/>
+      <c r="K53" s="33" t="inlineStr"/>
+      <c r="L53" s="33" t="inlineStr"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>第8段階</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D54" s="21" t="n">
+        <v>526</v>
+      </c>
+      <c r="E54" s="21" t="n">
+        <v>525</v>
+      </c>
+      <c r="F54" s="21" t="n">
+        <v>525</v>
+      </c>
+      <c r="G54" s="33" t="inlineStr"/>
+      <c r="H54" s="33" t="inlineStr"/>
+      <c r="I54" s="33" t="inlineStr"/>
+      <c r="J54" s="33" t="inlineStr"/>
+      <c r="K54" s="33" t="inlineStr"/>
+      <c r="L54" s="33" t="inlineStr"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>第9段階</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D55" s="21" t="n">
+        <v>202</v>
+      </c>
+      <c r="E55" s="21" t="n">
+        <v>202</v>
+      </c>
+      <c r="F55" s="21" t="n">
+        <v>202</v>
+      </c>
+      <c r="G55" s="33" t="inlineStr"/>
+      <c r="H55" s="33" t="inlineStr"/>
+      <c r="I55" s="33" t="inlineStr"/>
+      <c r="J55" s="33" t="inlineStr"/>
+      <c r="K55" s="33" t="inlineStr"/>
+      <c r="L55" s="33" t="inlineStr"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>第10段階</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D56" s="21" t="n">
+        <v>99</v>
+      </c>
+      <c r="E56" s="21" t="n">
+        <v>99</v>
+      </c>
+      <c r="F56" s="21" t="n">
+        <v>100</v>
+      </c>
+      <c r="G56" s="33" t="inlineStr"/>
+      <c r="H56" s="33" t="inlineStr"/>
+      <c r="I56" s="33" t="inlineStr"/>
+      <c r="J56" s="33" t="inlineStr"/>
+      <c r="K56" s="33" t="inlineStr"/>
+      <c r="L56" s="33" t="inlineStr"/>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>第11段階</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D57" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="E57" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="F57" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="G57" s="33" t="inlineStr"/>
+      <c r="H57" s="33" t="inlineStr"/>
+      <c r="I57" s="33" t="inlineStr"/>
+      <c r="J57" s="33" t="inlineStr"/>
+      <c r="K57" s="33" t="inlineStr"/>
+      <c r="L57" s="33" t="inlineStr"/>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>第12段階</t>
+        </is>
+      </c>
+      <c r="C58" s="15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D58" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="E58" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="F58" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="G58" s="33" t="inlineStr"/>
+      <c r="H58" s="33" t="inlineStr"/>
+      <c r="I58" s="33" t="inlineStr"/>
+      <c r="J58" s="33" t="inlineStr"/>
+      <c r="K58" s="33" t="inlineStr"/>
+      <c r="L58" s="33" t="inlineStr"/>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>第13段階</t>
+        </is>
+      </c>
+      <c r="C59" s="15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D59" s="21" t="n">
+        <v>108</v>
+      </c>
+      <c r="E59" s="21" t="n">
+        <v>108</v>
+      </c>
+      <c r="F59" s="21" t="n">
+        <v>108</v>
+      </c>
+      <c r="G59" s="33" t="inlineStr"/>
+      <c r="H59" s="33" t="inlineStr"/>
+      <c r="I59" s="33" t="inlineStr"/>
+      <c r="J59" s="33" t="inlineStr"/>
+      <c r="K59" s="33" t="inlineStr"/>
+      <c r="L59" s="33" t="inlineStr"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="23" t="inlineStr"/>
+      <c r="B60" s="23" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="C60" s="24" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D60" s="25" t="n">
+        <v>9116</v>
+      </c>
+      <c r="E60" s="25" t="n">
+        <v>9110</v>
+      </c>
+      <c r="F60" s="25" t="n">
+        <v>9107</v>
+      </c>
+      <c r="G60" s="34" t="inlineStr"/>
+      <c r="H60" s="34" t="inlineStr"/>
+      <c r="I60" s="34" t="inlineStr"/>
+      <c r="J60" s="34" t="inlineStr"/>
+      <c r="K60" s="34" t="inlineStr"/>
+      <c r="L60" s="34" t="inlineStr"/>
+    </row>
+    <row r="61" ht="76" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>注1）本表の値は必要資料が未受領であることによる暫定値です。確定値ではありません。
+注2）人口の設定を案Cに改めないまま入れる場合の値です。構成比は1の表と同じ（令和6年度の実績）で、合計だけを画面が表示している第1号被保険者数に合わせています。
+注3）この場合、システムが出す保険料額は当方の算定とは別のものになります。人口も給付費の見込みも当方の算定と違うためです。画面の値と当方の値を突き合わせるときは、先に人口の設定を案Cに改めてください（確認事項No.127）。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
+    <mergeCell ref="A26:L26"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A43:L43"/>
     <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A45:L45"/>
+    <mergeCell ref="A61:L61"/>
     <mergeCell ref="A4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
+++ b/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
@@ -28,9 +28,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -137,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -233,10 +234,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2556,7 +2554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3057,27 +3055,77 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="9" t="inlineStr"/>
-      <c r="B23" s="9" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>画面の第1号被保険者数に合わせる表の計が画面の値と一致すること</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>08シート3の各年度で Σ段階別 ＝ 画面の第1号被保険者数</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>全8年度（令和9年度・令和10年度・令和11年度・令和12年度・令和17年度・令和22年度・令和27年度・令和32年度）／合わない なし</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>画面の写しの年度が算定の年度と過不足なく一致すること</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>GAMEN13_HIHO のキー ＝ 令和9〜12・17・22・27・32年度</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>画面の写し8年度／算定8年度</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="9" t="inlineStr"/>
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>自己点検の結果</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr"/>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>適合18件・不適合0件</t>
-        </is>
-      </c>
-      <c r="E23" s="26" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr"/>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>適合20件・不適合0件</t>
+        </is>
+      </c>
+      <c r="E25" s="26" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>注）本シートは点検の記録であり、本表の値が暫定値であることを変えるものではありません。点検しているのは内的整合であって、未受領の資料により値が動くことは点検では解消しません。</t>
         </is>
@@ -3087,7 +3135,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A26:E26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
@@ -3180,7 +3228,7 @@
           <t>同じ</t>
         </is>
       </c>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="E6" s="34" t="inlineStr">
         <is>
           <t>変わらない</t>
         </is>
@@ -3205,7 +3253,7 @@
           <t>同じ</t>
         </is>
       </c>
-      <c r="E7" s="35" t="inlineStr">
+      <c r="E7" s="34" t="inlineStr">
         <is>
           <t>変わらない</t>
         </is>
@@ -3230,7 +3278,7 @@
           <t>同じ</t>
         </is>
       </c>
-      <c r="E8" s="35" t="inlineStr">
+      <c r="E8" s="34" t="inlineStr">
         <is>
           <t>変わらない</t>
         </is>
@@ -3255,7 +3303,7 @@
           <t>同じ</t>
         </is>
       </c>
-      <c r="E9" s="35" t="inlineStr">
+      <c r="E9" s="34" t="inlineStr">
         <is>
           <t>変わらない</t>
         </is>
@@ -3280,7 +3328,7 @@
           <t>同じ（据え置きのまま）</t>
         </is>
       </c>
-      <c r="E10" s="35" t="inlineStr">
+      <c r="E10" s="34" t="inlineStr">
         <is>
           <t>変わらない</t>
         </is>
@@ -3305,7 +3353,7 @@
           <t>9,031,900,444円</t>
         </is>
       </c>
-      <c r="E11" s="35" t="inlineStr">
+      <c r="E11" s="34" t="inlineStr">
         <is>
           <t>変わらない</t>
         </is>
@@ -3330,7 +3378,7 @@
           <t>6,436円</t>
         </is>
       </c>
-      <c r="E12" s="35" t="inlineStr">
+      <c r="E12" s="34" t="inlineStr">
         <is>
           <t>変わらない</t>
         </is>
@@ -3355,7 +3403,7 @@
           <t>6,400円</t>
         </is>
       </c>
-      <c r="E13" s="35" t="inlineStr">
+      <c r="E13" s="34" t="inlineStr">
         <is>
           <t>変わらない</t>
         </is>
@@ -3443,7 +3491,7 @@
           <t>影響しない</t>
         </is>
       </c>
-      <c r="E19" s="35" t="inlineStr">
+      <c r="E19" s="34" t="inlineStr">
         <is>
           <t>直す必要がない</t>
         </is>
@@ -3468,7 +3516,7 @@
           <t>影響しない</t>
         </is>
       </c>
-      <c r="E20" s="35" t="inlineStr">
+      <c r="E20" s="34" t="inlineStr">
         <is>
           <t>直す必要がない</t>
         </is>
@@ -3493,7 +3541,7 @@
           <t>影響しない</t>
         </is>
       </c>
-      <c r="E21" s="35" t="inlineStr">
+      <c r="E21" s="34" t="inlineStr">
         <is>
           <t>直す必要がない</t>
         </is>
@@ -19971,7 +20019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -21527,12 +21575,36 @@
           <t>令和11年度</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="5" t="inlineStr"/>
-      <c r="L46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>基準所得金額</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="6" t="n">
@@ -21555,12 +21627,26 @@
       <c r="F47" s="21" t="n">
         <v>1456</v>
       </c>
-      <c r="G47" s="33" t="inlineStr"/>
-      <c r="H47" s="33" t="inlineStr"/>
-      <c r="I47" s="33" t="inlineStr"/>
-      <c r="J47" s="33" t="inlineStr"/>
-      <c r="K47" s="33" t="inlineStr"/>
-      <c r="L47" s="33" t="inlineStr"/>
+      <c r="G47" s="21" t="n">
+        <v>1456</v>
+      </c>
+      <c r="H47" s="21" t="n">
+        <v>1465</v>
+      </c>
+      <c r="I47" s="21" t="n">
+        <v>1499</v>
+      </c>
+      <c r="J47" s="21" t="n">
+        <v>1482</v>
+      </c>
+      <c r="K47" s="21" t="n">
+        <v>1438</v>
+      </c>
+      <c r="L47" s="22" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="6" t="n">
@@ -21583,12 +21669,26 @@
       <c r="F48" s="21" t="n">
         <v>1172</v>
       </c>
-      <c r="G48" s="33" t="inlineStr"/>
-      <c r="H48" s="33" t="inlineStr"/>
-      <c r="I48" s="33" t="inlineStr"/>
-      <c r="J48" s="33" t="inlineStr"/>
-      <c r="K48" s="33" t="inlineStr"/>
-      <c r="L48" s="33" t="inlineStr"/>
+      <c r="G48" s="21" t="n">
+        <v>1172</v>
+      </c>
+      <c r="H48" s="21" t="n">
+        <v>1180</v>
+      </c>
+      <c r="I48" s="21" t="n">
+        <v>1207</v>
+      </c>
+      <c r="J48" s="21" t="n">
+        <v>1193</v>
+      </c>
+      <c r="K48" s="21" t="n">
+        <v>1158</v>
+      </c>
+      <c r="L48" s="22" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="6" t="n">
@@ -21611,12 +21711,26 @@
       <c r="F49" s="21" t="n">
         <v>933</v>
       </c>
-      <c r="G49" s="33" t="inlineStr"/>
-      <c r="H49" s="33" t="inlineStr"/>
-      <c r="I49" s="33" t="inlineStr"/>
-      <c r="J49" s="33" t="inlineStr"/>
-      <c r="K49" s="33" t="inlineStr"/>
-      <c r="L49" s="33" t="inlineStr"/>
+      <c r="G49" s="21" t="n">
+        <v>933</v>
+      </c>
+      <c r="H49" s="21" t="n">
+        <v>939</v>
+      </c>
+      <c r="I49" s="21" t="n">
+        <v>960</v>
+      </c>
+      <c r="J49" s="21" t="n">
+        <v>950</v>
+      </c>
+      <c r="K49" s="21" t="n">
+        <v>921</v>
+      </c>
+      <c r="L49" s="22" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="6" t="n">
@@ -21639,12 +21753,26 @@
       <c r="F50" s="21" t="n">
         <v>750</v>
       </c>
-      <c r="G50" s="33" t="inlineStr"/>
-      <c r="H50" s="33" t="inlineStr"/>
-      <c r="I50" s="33" t="inlineStr"/>
-      <c r="J50" s="33" t="inlineStr"/>
-      <c r="K50" s="33" t="inlineStr"/>
-      <c r="L50" s="33" t="inlineStr"/>
+      <c r="G50" s="21" t="n">
+        <v>750</v>
+      </c>
+      <c r="H50" s="21" t="n">
+        <v>755</v>
+      </c>
+      <c r="I50" s="21" t="n">
+        <v>772</v>
+      </c>
+      <c r="J50" s="21" t="n">
+        <v>763</v>
+      </c>
+      <c r="K50" s="21" t="n">
+        <v>740</v>
+      </c>
+      <c r="L50" s="22" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="6" t="n">
@@ -21667,12 +21795,26 @@
       <c r="F51" s="21" t="n">
         <v>1179</v>
       </c>
-      <c r="G51" s="33" t="inlineStr"/>
-      <c r="H51" s="33" t="inlineStr"/>
-      <c r="I51" s="33" t="inlineStr"/>
-      <c r="J51" s="33" t="inlineStr"/>
-      <c r="K51" s="33" t="inlineStr"/>
-      <c r="L51" s="33" t="inlineStr"/>
+      <c r="G51" s="21" t="n">
+        <v>1179</v>
+      </c>
+      <c r="H51" s="21" t="n">
+        <v>1187</v>
+      </c>
+      <c r="I51" s="21" t="n">
+        <v>1214</v>
+      </c>
+      <c r="J51" s="21" t="n">
+        <v>1201</v>
+      </c>
+      <c r="K51" s="21" t="n">
+        <v>1165</v>
+      </c>
+      <c r="L51" s="22" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="6" t="n">
@@ -21695,12 +21837,26 @@
       <c r="F52" s="21" t="n">
         <v>1376</v>
       </c>
-      <c r="G52" s="33" t="inlineStr"/>
-      <c r="H52" s="33" t="inlineStr"/>
-      <c r="I52" s="33" t="inlineStr"/>
-      <c r="J52" s="33" t="inlineStr"/>
-      <c r="K52" s="33" t="inlineStr"/>
-      <c r="L52" s="33" t="inlineStr"/>
+      <c r="G52" s="21" t="n">
+        <v>1376</v>
+      </c>
+      <c r="H52" s="21" t="n">
+        <v>1385</v>
+      </c>
+      <c r="I52" s="21" t="n">
+        <v>1417</v>
+      </c>
+      <c r="J52" s="21" t="n">
+        <v>1401</v>
+      </c>
+      <c r="K52" s="21" t="n">
+        <v>1359</v>
+      </c>
+      <c r="L52" s="22" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="6" t="n">
@@ -21723,12 +21879,24 @@
       <c r="F53" s="21" t="n">
         <v>1228</v>
       </c>
-      <c r="G53" s="33" t="inlineStr"/>
-      <c r="H53" s="33" t="inlineStr"/>
-      <c r="I53" s="33" t="inlineStr"/>
-      <c r="J53" s="33" t="inlineStr"/>
-      <c r="K53" s="33" t="inlineStr"/>
-      <c r="L53" s="33" t="inlineStr"/>
+      <c r="G53" s="21" t="n">
+        <v>1228</v>
+      </c>
+      <c r="H53" s="21" t="n">
+        <v>1236</v>
+      </c>
+      <c r="I53" s="21" t="n">
+        <v>1264</v>
+      </c>
+      <c r="J53" s="21" t="n">
+        <v>1250</v>
+      </c>
+      <c r="K53" s="21" t="n">
+        <v>1213</v>
+      </c>
+      <c r="L53" s="22" t="n">
+        <v>1200000</v>
+      </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="6" t="n">
@@ -21751,12 +21919,24 @@
       <c r="F54" s="21" t="n">
         <v>525</v>
       </c>
-      <c r="G54" s="33" t="inlineStr"/>
-      <c r="H54" s="33" t="inlineStr"/>
-      <c r="I54" s="33" t="inlineStr"/>
-      <c r="J54" s="33" t="inlineStr"/>
-      <c r="K54" s="33" t="inlineStr"/>
-      <c r="L54" s="33" t="inlineStr"/>
+      <c r="G54" s="21" t="n">
+        <v>525</v>
+      </c>
+      <c r="H54" s="21" t="n">
+        <v>529</v>
+      </c>
+      <c r="I54" s="21" t="n">
+        <v>540</v>
+      </c>
+      <c r="J54" s="21" t="n">
+        <v>534</v>
+      </c>
+      <c r="K54" s="21" t="n">
+        <v>518</v>
+      </c>
+      <c r="L54" s="22" t="n">
+        <v>2100000</v>
+      </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="6" t="n">
@@ -21779,12 +21959,24 @@
       <c r="F55" s="21" t="n">
         <v>202</v>
       </c>
-      <c r="G55" s="33" t="inlineStr"/>
-      <c r="H55" s="33" t="inlineStr"/>
-      <c r="I55" s="33" t="inlineStr"/>
-      <c r="J55" s="33" t="inlineStr"/>
-      <c r="K55" s="33" t="inlineStr"/>
-      <c r="L55" s="33" t="inlineStr"/>
+      <c r="G55" s="21" t="n">
+        <v>202</v>
+      </c>
+      <c r="H55" s="21" t="n">
+        <v>203</v>
+      </c>
+      <c r="I55" s="21" t="n">
+        <v>208</v>
+      </c>
+      <c r="J55" s="21" t="n">
+        <v>206</v>
+      </c>
+      <c r="K55" s="21" t="n">
+        <v>199</v>
+      </c>
+      <c r="L55" s="22" t="n">
+        <v>3200000</v>
+      </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="6" t="n">
@@ -21807,12 +21999,24 @@
       <c r="F56" s="21" t="n">
         <v>100</v>
       </c>
-      <c r="G56" s="33" t="inlineStr"/>
-      <c r="H56" s="33" t="inlineStr"/>
-      <c r="I56" s="33" t="inlineStr"/>
-      <c r="J56" s="33" t="inlineStr"/>
-      <c r="K56" s="33" t="inlineStr"/>
-      <c r="L56" s="33" t="inlineStr"/>
+      <c r="G56" s="21" t="n">
+        <v>99</v>
+      </c>
+      <c r="H56" s="21" t="n">
+        <v>100</v>
+      </c>
+      <c r="I56" s="21" t="n">
+        <v>102</v>
+      </c>
+      <c r="J56" s="21" t="n">
+        <v>101</v>
+      </c>
+      <c r="K56" s="21" t="n">
+        <v>98</v>
+      </c>
+      <c r="L56" s="22" t="n">
+        <v>4200000</v>
+      </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="6" t="n">
@@ -21835,12 +22039,24 @@
       <c r="F57" s="21" t="n">
         <v>54</v>
       </c>
-      <c r="G57" s="33" t="inlineStr"/>
-      <c r="H57" s="33" t="inlineStr"/>
-      <c r="I57" s="33" t="inlineStr"/>
-      <c r="J57" s="33" t="inlineStr"/>
-      <c r="K57" s="33" t="inlineStr"/>
-      <c r="L57" s="33" t="inlineStr"/>
+      <c r="G57" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="H57" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="I57" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="J57" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="K57" s="21" t="n">
+        <v>53</v>
+      </c>
+      <c r="L57" s="22" t="n">
+        <v>5200000</v>
+      </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="6" t="n">
@@ -21863,12 +22079,24 @@
       <c r="F58" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="G58" s="33" t="inlineStr"/>
-      <c r="H58" s="33" t="inlineStr"/>
-      <c r="I58" s="33" t="inlineStr"/>
-      <c r="J58" s="33" t="inlineStr"/>
-      <c r="K58" s="33" t="inlineStr"/>
-      <c r="L58" s="33" t="inlineStr"/>
+      <c r="G58" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="H58" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="I58" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="J58" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="K58" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="L58" s="22" t="n">
+        <v>6200000</v>
+      </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="6" t="n">
@@ -21891,12 +22119,24 @@
       <c r="F59" s="21" t="n">
         <v>108</v>
       </c>
-      <c r="G59" s="33" t="inlineStr"/>
-      <c r="H59" s="33" t="inlineStr"/>
-      <c r="I59" s="33" t="inlineStr"/>
-      <c r="J59" s="33" t="inlineStr"/>
-      <c r="K59" s="33" t="inlineStr"/>
-      <c r="L59" s="33" t="inlineStr"/>
+      <c r="G59" s="21" t="n">
+        <v>108</v>
+      </c>
+      <c r="H59" s="21" t="n">
+        <v>109</v>
+      </c>
+      <c r="I59" s="21" t="n">
+        <v>112</v>
+      </c>
+      <c r="J59" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="K59" s="21" t="n">
+        <v>107</v>
+      </c>
+      <c r="L59" s="22" t="n">
+        <v>7200000</v>
+      </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="23" t="inlineStr"/>
@@ -21919,19 +22159,76 @@
       <c r="F60" s="25" t="n">
         <v>9107</v>
       </c>
-      <c r="G60" s="34" t="inlineStr"/>
-      <c r="H60" s="34" t="inlineStr"/>
-      <c r="I60" s="34" t="inlineStr"/>
-      <c r="J60" s="34" t="inlineStr"/>
-      <c r="K60" s="34" t="inlineStr"/>
-      <c r="L60" s="34" t="inlineStr"/>
-    </row>
-    <row r="61" ht="76" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="G60" s="25" t="n">
+        <v>9106</v>
+      </c>
+      <c r="H60" s="25" t="n">
+        <v>9166</v>
+      </c>
+      <c r="I60" s="25" t="n">
+        <v>9375</v>
+      </c>
+      <c r="J60" s="25" t="n">
+        <v>9270</v>
+      </c>
+      <c r="K60" s="25" t="n">
+        <v>8993</v>
+      </c>
+      <c r="L60" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="13" t="inlineStr"/>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>画面と案Cの差（案C−画面）</t>
+        </is>
+      </c>
+      <c r="C61" s="30" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D61" s="33" t="n">
+        <v>31</v>
+      </c>
+      <c r="E61" s="33" t="n">
+        <v>69</v>
+      </c>
+      <c r="F61" s="33" t="n">
+        <v>106</v>
+      </c>
+      <c r="G61" s="33" t="n">
+        <v>105</v>
+      </c>
+      <c r="H61" s="33" t="n">
+        <v>84</v>
+      </c>
+      <c r="I61" s="33" t="n">
+        <v>116</v>
+      </c>
+      <c r="J61" s="33" t="n">
+        <v>125</v>
+      </c>
+      <c r="K61" s="33" t="n">
+        <v>134</v>
+      </c>
+      <c r="L61" s="32" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="90" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>注1）本表の値は必要資料が未受領であることによる暫定値です。確定値ではありません。
 注2）人口の設定を案Cに改めないまま入れる場合の値です。構成比は1の表と同じ（令和6年度の実績）で、合計だけを画面が表示している第1号被保険者数に合わせています。
-注3）この場合、システムが出す保険料額は当方の算定とは別のものになります。人口も給付費の見込みも当方の算定と違うためです。画面の値と当方の値を突き合わせるときは、先に人口の設定を案Cに改めてください（確認事項No.127）。</t>
+注3）画面が表示する第1号被保険者数は令和12年度以降にもあります。「第10期」の画面が令和9年度から令和11年度、「令和12年度以降」の画面が令和12・17・22・27・32年度です。いずれも人口の設定が社人研のままのときの値であり、案Cとは+31人から+134人の開きがあります（いずれも案Cが上回ります）。
+注4）この場合、システムが出す保険料額は当方の算定とは別のものになります。人口も給付費の見込みも当方の算定と違うためです。画面の値と当方の値を突き合わせるときは、先に人口の設定を案Cに改めてください（確認事項No.127）。</t>
         </is>
       </c>
     </row>
@@ -21943,8 +22240,8 @@
     <mergeCell ref="A43:L43"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A45:L45"/>
-    <mergeCell ref="A61:L61"/>
     <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A62:L62"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>

--- a/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
+++ b/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
@@ -198,10 +198,10 @@
     <xf numFmtId="165" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -219,19 +219,19 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2554,7 +2554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3105,27 +3105,77 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="9" t="inlineStr"/>
-      <c r="B25" s="9" t="inlineStr">
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>基準所得金額が第7段階から第16段階の10件で昇順であること</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>第1〜6段階は None（画面も入力欄なし）／第7段階以降は金額かつ昇順</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>欄なし 第1・2・3・4・5・6段階／金額10件（1,200,000〜10,200,000円）</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>第7段階から第13段階の基準所得金額が画面の標準の額と一致すること</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>STAGE から求めた額 ＝ 「①標準段階区分・割合」の画面が表示する額</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>1,200,000・2,100,000・3,200,000・4,200,000・5,200,000・6,200,000・7,200,000／画面 一致</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="9" t="inlineStr"/>
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>自己点検の結果</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr"/>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>適合20件・不適合0件</t>
-        </is>
-      </c>
-      <c r="E25" s="26" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr"/>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>適合22件・不適合0件</t>
+        </is>
+      </c>
+      <c r="E27" s="26" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>注）本シートは点検の記録であり、本表の値が暫定値であることを変えるものではありません。点検しているのは内的整合であって、未受領の資料により値が動くことは点検では解消しません。</t>
         </is>
@@ -3133,9 +3183,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A26:E26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
@@ -20019,13 +20069,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L62"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -20034,6 +20084,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -20054,7 +20105,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>1　所得段階別第1号被保険者数（人）</t>
+          <t>1　所得段階別第1号被保険者数（人）・割合・基準所得金額</t>
         </is>
       </c>
     </row>
@@ -20067,50 +20118,55 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>乗率</t>
+          <t>割合</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
+          <t>基準所得金額（円）</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
           <t>令和9年度</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>令和10年度</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>令和11年度</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>令和12年度</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>令和17年度</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>令和22年度</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>令和27年度</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>令和32年度</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>R7実績</t>
         </is>
@@ -20120,39 +20176,44 @@
       <c r="A6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>第1段階</t>
         </is>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="16" t="n">
         <v>0.455</v>
       </c>
-      <c r="D6" s="21" t="n">
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="n">
         <v>1462</v>
       </c>
-      <c r="E6" s="21" t="n">
+      <c r="F6" s="22" t="n">
         <v>1467</v>
       </c>
-      <c r="F6" s="21" t="n">
+      <c r="G6" s="22" t="n">
         <v>1473</v>
       </c>
-      <c r="G6" s="21" t="n">
+      <c r="H6" s="22" t="n">
         <v>1473</v>
       </c>
-      <c r="H6" s="21" t="n">
+      <c r="I6" s="22" t="n">
         <v>1479</v>
       </c>
-      <c r="I6" s="21" t="n">
+      <c r="J6" s="22" t="n">
         <v>1517</v>
       </c>
-      <c r="J6" s="21" t="n">
+      <c r="K6" s="22" t="n">
         <v>1502</v>
       </c>
-      <c r="K6" s="21" t="n">
+      <c r="L6" s="22" t="n">
         <v>1459</v>
       </c>
-      <c r="L6" s="22" t="n">
+      <c r="M6" s="21" t="n">
         <v>1385</v>
       </c>
     </row>
@@ -20160,39 +20221,44 @@
       <c r="A7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>第2段階</t>
         </is>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="16" t="n">
         <v>0.639</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="n">
         <v>1178</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="F7" s="22" t="n">
         <v>1182</v>
       </c>
-      <c r="F7" s="21" t="n">
+      <c r="G7" s="22" t="n">
         <v>1186</v>
       </c>
-      <c r="G7" s="21" t="n">
+      <c r="H7" s="22" t="n">
         <v>1186</v>
       </c>
-      <c r="H7" s="21" t="n">
+      <c r="I7" s="22" t="n">
         <v>1191</v>
       </c>
-      <c r="I7" s="21" t="n">
+      <c r="J7" s="22" t="n">
         <v>1222</v>
       </c>
-      <c r="J7" s="21" t="n">
+      <c r="K7" s="22" t="n">
         <v>1209</v>
       </c>
-      <c r="K7" s="21" t="n">
+      <c r="L7" s="22" t="n">
         <v>1175</v>
       </c>
-      <c r="L7" s="22" t="n">
+      <c r="M7" s="21" t="n">
         <v>1141</v>
       </c>
     </row>
@@ -20200,39 +20266,44 @@
       <c r="A8" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>第3段階</t>
         </is>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="16" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="n">
         <v>937</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="F8" s="22" t="n">
         <v>940</v>
       </c>
-      <c r="F8" s="21" t="n">
+      <c r="G8" s="22" t="n">
         <v>944</v>
       </c>
-      <c r="G8" s="21" t="n">
+      <c r="H8" s="22" t="n">
         <v>944</v>
       </c>
-      <c r="H8" s="21" t="n">
+      <c r="I8" s="22" t="n">
         <v>947</v>
       </c>
-      <c r="I8" s="21" t="n">
+      <c r="J8" s="22" t="n">
         <v>972</v>
       </c>
-      <c r="J8" s="21" t="n">
+      <c r="K8" s="22" t="n">
         <v>962</v>
       </c>
-      <c r="K8" s="21" t="n">
+      <c r="L8" s="22" t="n">
         <v>935</v>
       </c>
-      <c r="L8" s="22" t="n">
+      <c r="M8" s="21" t="n">
         <v>887</v>
       </c>
     </row>
@@ -20245,34 +20316,39 @@
           <t>第4段階</t>
         </is>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="16" t="n">
         <v>0.86</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="n">
         <v>753</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="F9" s="22" t="n">
         <v>756</v>
       </c>
-      <c r="F9" s="21" t="n">
+      <c r="G9" s="22" t="n">
         <v>759</v>
       </c>
-      <c r="G9" s="21" t="n">
+      <c r="H9" s="22" t="n">
         <v>758</v>
       </c>
-      <c r="H9" s="21" t="n">
+      <c r="I9" s="22" t="n">
         <v>762</v>
       </c>
-      <c r="I9" s="21" t="n">
+      <c r="J9" s="22" t="n">
         <v>782</v>
       </c>
-      <c r="J9" s="21" t="n">
+      <c r="K9" s="22" t="n">
         <v>773</v>
       </c>
-      <c r="K9" s="21" t="n">
+      <c r="L9" s="22" t="n">
         <v>751</v>
       </c>
-      <c r="L9" s="22" t="n">
+      <c r="M9" s="21" t="n">
         <v>704</v>
       </c>
     </row>
@@ -20285,34 +20361,39 @@
           <t>第5段階（基準）</t>
         </is>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="n">
         <v>1185</v>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="F10" s="22" t="n">
         <v>1189</v>
       </c>
-      <c r="F10" s="21" t="n">
+      <c r="G10" s="22" t="n">
         <v>1193</v>
       </c>
-      <c r="G10" s="21" t="n">
+      <c r="H10" s="22" t="n">
         <v>1193</v>
       </c>
-      <c r="H10" s="21" t="n">
+      <c r="I10" s="22" t="n">
         <v>1198</v>
       </c>
-      <c r="I10" s="21" t="n">
+      <c r="J10" s="22" t="n">
         <v>1229</v>
       </c>
-      <c r="J10" s="21" t="n">
+      <c r="K10" s="22" t="n">
         <v>1217</v>
       </c>
-      <c r="K10" s="21" t="n">
+      <c r="L10" s="22" t="n">
         <v>1182</v>
       </c>
-      <c r="L10" s="22" t="n">
+      <c r="M10" s="21" t="n">
         <v>1202</v>
       </c>
     </row>
@@ -20325,34 +20406,39 @@
           <t>第6段階</t>
         </is>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="16" t="n">
         <v>1.26</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="n">
         <v>1382</v>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="F11" s="22" t="n">
         <v>1387</v>
       </c>
-      <c r="F11" s="21" t="n">
+      <c r="G11" s="22" t="n">
         <v>1392</v>
       </c>
-      <c r="G11" s="21" t="n">
+      <c r="H11" s="22" t="n">
         <v>1392</v>
       </c>
-      <c r="H11" s="21" t="n">
+      <c r="I11" s="22" t="n">
         <v>1398</v>
       </c>
-      <c r="I11" s="21" t="n">
+      <c r="J11" s="22" t="n">
         <v>1434</v>
       </c>
-      <c r="J11" s="21" t="n">
+      <c r="K11" s="22" t="n">
         <v>1420</v>
       </c>
-      <c r="K11" s="21" t="n">
+      <c r="L11" s="22" t="n">
         <v>1379</v>
       </c>
-      <c r="L11" s="22" t="n">
+      <c r="M11" s="21" t="n">
         <v>1363</v>
       </c>
     </row>
@@ -20365,34 +20451,37 @@
           <t>第7段階</t>
         </is>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="C12" s="16" t="n">
         <v>1.31</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="22" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="E12" s="22" t="n">
         <v>1233</v>
       </c>
-      <c r="E12" s="21" t="n">
+      <c r="F12" s="22" t="n">
         <v>1238</v>
       </c>
-      <c r="F12" s="21" t="n">
+      <c r="G12" s="22" t="n">
         <v>1243</v>
       </c>
-      <c r="G12" s="21" t="n">
+      <c r="H12" s="22" t="n">
         <v>1242</v>
       </c>
-      <c r="H12" s="21" t="n">
+      <c r="I12" s="22" t="n">
         <v>1247</v>
       </c>
-      <c r="I12" s="21" t="n">
+      <c r="J12" s="22" t="n">
         <v>1280</v>
       </c>
-      <c r="J12" s="21" t="n">
+      <c r="K12" s="22" t="n">
         <v>1267</v>
       </c>
-      <c r="K12" s="21" t="n">
+      <c r="L12" s="22" t="n">
         <v>1231</v>
       </c>
-      <c r="L12" s="22" t="n">
+      <c r="M12" s="21" t="n">
         <v>1261</v>
       </c>
     </row>
@@ -20405,34 +20494,37 @@
           <t>第8段階</t>
         </is>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="16" t="n">
         <v>1.59</v>
       </c>
-      <c r="D13" s="21" t="n">
+      <c r="D13" s="22" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="E13" s="22" t="n">
         <v>527</v>
       </c>
-      <c r="E13" s="21" t="n">
+      <c r="F13" s="22" t="n">
         <v>529</v>
       </c>
-      <c r="F13" s="21" t="n">
+      <c r="G13" s="22" t="n">
         <v>531</v>
       </c>
-      <c r="G13" s="21" t="n">
+      <c r="H13" s="22" t="n">
         <v>531</v>
       </c>
-      <c r="H13" s="21" t="n">
+      <c r="I13" s="22" t="n">
         <v>533</v>
       </c>
-      <c r="I13" s="21" t="n">
+      <c r="J13" s="22" t="n">
         <v>547</v>
       </c>
-      <c r="J13" s="21" t="n">
+      <c r="K13" s="22" t="n">
         <v>542</v>
       </c>
-      <c r="K13" s="21" t="n">
+      <c r="L13" s="22" t="n">
         <v>526</v>
       </c>
-      <c r="L13" s="22" t="n">
+      <c r="M13" s="21" t="n">
         <v>550</v>
       </c>
     </row>
@@ -20445,34 +20537,37 @@
           <t>第9段階</t>
         </is>
       </c>
-      <c r="C14" s="15" t="n">
+      <c r="C14" s="16" t="n">
         <v>1.63</v>
       </c>
-      <c r="D14" s="21" t="n">
+      <c r="D14" s="22" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="E14" s="22" t="n">
         <v>203</v>
       </c>
-      <c r="E14" s="21" t="n">
+      <c r="F14" s="22" t="n">
         <v>204</v>
       </c>
-      <c r="F14" s="21" t="n">
+      <c r="G14" s="22" t="n">
         <v>204</v>
       </c>
-      <c r="G14" s="21" t="n">
+      <c r="H14" s="22" t="n">
         <v>204</v>
       </c>
-      <c r="H14" s="21" t="n">
+      <c r="I14" s="22" t="n">
         <v>205</v>
       </c>
-      <c r="I14" s="21" t="n">
+      <c r="J14" s="22" t="n">
         <v>210</v>
       </c>
-      <c r="J14" s="21" t="n">
+      <c r="K14" s="22" t="n">
         <v>208</v>
       </c>
-      <c r="K14" s="21" t="n">
+      <c r="L14" s="22" t="n">
         <v>202</v>
       </c>
-      <c r="L14" s="22" t="n">
+      <c r="M14" s="21" t="n">
         <v>238</v>
       </c>
     </row>
@@ -20485,34 +20580,37 @@
           <t>第10段階</t>
         </is>
       </c>
-      <c r="C15" s="15" t="n">
+      <c r="C15" s="16" t="n">
         <v>1.9</v>
       </c>
-      <c r="D15" s="21" t="n">
+      <c r="D15" s="22" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="E15" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="E15" s="21" t="n">
+      <c r="F15" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="F15" s="21" t="n">
+      <c r="G15" s="22" t="n">
         <v>101</v>
       </c>
-      <c r="G15" s="21" t="n">
+      <c r="H15" s="22" t="n">
         <v>101</v>
       </c>
-      <c r="H15" s="21" t="n">
+      <c r="I15" s="22" t="n">
         <v>101</v>
       </c>
-      <c r="I15" s="21" t="n">
+      <c r="J15" s="22" t="n">
         <v>104</v>
       </c>
-      <c r="J15" s="21" t="n">
+      <c r="K15" s="22" t="n">
         <v>103</v>
       </c>
-      <c r="K15" s="21" t="n">
+      <c r="L15" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="L15" s="22" t="n">
+      <c r="M15" s="21" t="n">
         <v>105</v>
       </c>
     </row>
@@ -20525,34 +20623,37 @@
           <t>第11段階</t>
         </is>
       </c>
-      <c r="C16" s="15" t="n">
+      <c r="C16" s="16" t="n">
         <v>2.165</v>
       </c>
-      <c r="D16" s="21" t="n">
+      <c r="D16" s="22" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="E16" s="22" t="n">
         <v>54</v>
       </c>
-      <c r="E16" s="21" t="n">
+      <c r="F16" s="22" t="n">
         <v>54</v>
       </c>
-      <c r="F16" s="21" t="n">
+      <c r="G16" s="22" t="n">
         <v>54</v>
       </c>
-      <c r="G16" s="21" t="n">
+      <c r="H16" s="22" t="n">
         <v>54</v>
       </c>
-      <c r="H16" s="21" t="n">
+      <c r="I16" s="22" t="n">
         <v>55</v>
       </c>
-      <c r="I16" s="21" t="n">
+      <c r="J16" s="22" t="n">
         <v>56</v>
       </c>
-      <c r="J16" s="21" t="n">
+      <c r="K16" s="22" t="n">
         <v>55</v>
       </c>
-      <c r="K16" s="21" t="n">
+      <c r="L16" s="22" t="n">
         <v>54</v>
       </c>
-      <c r="L16" s="22" t="n">
+      <c r="M16" s="21" t="n">
         <v>58</v>
       </c>
     </row>
@@ -20565,34 +20666,37 @@
           <t>第12段階</t>
         </is>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C17" s="16" t="n">
         <v>2.365</v>
       </c>
-      <c r="D17" s="21" t="n">
+      <c r="D17" s="22" t="n">
+        <v>6200000</v>
+      </c>
+      <c r="E17" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="E17" s="21" t="n">
+      <c r="F17" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="F17" s="21" t="n">
+      <c r="G17" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="G17" s="21" t="n">
+      <c r="H17" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="H17" s="21" t="n">
+      <c r="I17" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="I17" s="21" t="n">
+      <c r="J17" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="J17" s="21" t="n">
+      <c r="K17" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="K17" s="21" t="n">
+      <c r="L17" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="L17" s="22" t="n">
+      <c r="M17" s="21" t="n">
         <v>37</v>
       </c>
     </row>
@@ -20605,34 +20709,37 @@
           <t>第13段階</t>
         </is>
       </c>
-      <c r="C18" s="15" t="n">
+      <c r="C18" s="16" t="n">
         <v>2.565</v>
       </c>
-      <c r="D18" s="21" t="n">
+      <c r="D18" s="22" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="E18" s="22" t="n">
         <v>21</v>
       </c>
-      <c r="E18" s="21" t="n">
+      <c r="F18" s="22" t="n">
         <v>21</v>
       </c>
-      <c r="F18" s="21" t="n">
+      <c r="G18" s="22" t="n">
         <v>21</v>
       </c>
-      <c r="G18" s="21" t="n">
+      <c r="H18" s="22" t="n">
         <v>21</v>
       </c>
-      <c r="H18" s="21" t="n">
+      <c r="I18" s="22" t="n">
         <v>21</v>
       </c>
-      <c r="I18" s="21" t="n">
+      <c r="J18" s="22" t="n">
         <v>22</v>
       </c>
-      <c r="J18" s="21" t="n">
+      <c r="K18" s="22" t="n">
         <v>22</v>
       </c>
-      <c r="K18" s="21" t="n">
+      <c r="L18" s="22" t="n">
         <v>21</v>
       </c>
-      <c r="L18" s="22" t="n">
+      <c r="M18" s="21" t="n">
         <v>27</v>
       </c>
     </row>
@@ -20645,34 +20752,37 @@
           <t>第14段階</t>
         </is>
       </c>
-      <c r="C19" s="15" t="n">
+      <c r="C19" s="16" t="n">
         <v>2.575</v>
       </c>
-      <c r="D19" s="21" t="n">
+      <c r="D19" s="22" t="n">
+        <v>8200000</v>
+      </c>
+      <c r="E19" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="E19" s="21" t="n">
+      <c r="F19" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="F19" s="21" t="n">
+      <c r="G19" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="G19" s="21" t="n">
+      <c r="H19" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="H19" s="21" t="n">
+      <c r="I19" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="I19" s="21" t="n">
+      <c r="J19" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="J19" s="21" t="n">
+      <c r="K19" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="K19" s="21" t="n">
+      <c r="L19" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="L19" s="22" t="n">
+      <c r="M19" s="21" t="n">
         <v>13</v>
       </c>
     </row>
@@ -20685,34 +20795,37 @@
           <t>第15段階</t>
         </is>
       </c>
-      <c r="C20" s="15" t="n">
+      <c r="C20" s="16" t="n">
         <v>2.585</v>
       </c>
-      <c r="D20" s="21" t="n">
+      <c r="D20" s="22" t="n">
+        <v>9200000</v>
+      </c>
+      <c r="E20" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="E20" s="21" t="n">
+      <c r="F20" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="F20" s="21" t="n">
+      <c r="G20" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="G20" s="21" t="n">
+      <c r="H20" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="H20" s="21" t="n">
+      <c r="I20" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="I20" s="21" t="n">
+      <c r="J20" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="J20" s="21" t="n">
+      <c r="K20" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="K20" s="21" t="n">
+      <c r="L20" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="L20" s="22" t="n">
+      <c r="M20" s="21" t="n">
         <v>14</v>
       </c>
     </row>
@@ -20725,34 +20838,37 @@
           <t>第16段階</t>
         </is>
       </c>
-      <c r="C21" s="15" t="n">
+      <c r="C21" s="16" t="n">
         <v>2.595</v>
       </c>
-      <c r="D21" s="21" t="n">
+      <c r="D21" s="22" t="n">
+        <v>10200000</v>
+      </c>
+      <c r="E21" s="22" t="n">
         <v>66</v>
       </c>
-      <c r="E21" s="21" t="n">
+      <c r="F21" s="22" t="n">
         <v>66</v>
       </c>
-      <c r="F21" s="21" t="n">
+      <c r="G21" s="22" t="n">
         <v>66</v>
       </c>
-      <c r="G21" s="21" t="n">
+      <c r="H21" s="22" t="n">
         <v>66</v>
       </c>
-      <c r="H21" s="21" t="n">
+      <c r="I21" s="22" t="n">
         <v>67</v>
       </c>
-      <c r="I21" s="21" t="n">
+      <c r="J21" s="22" t="n">
         <v>68</v>
       </c>
-      <c r="J21" s="21" t="n">
+      <c r="K21" s="22" t="n">
         <v>68</v>
       </c>
-      <c r="K21" s="21" t="n">
+      <c r="L21" s="22" t="n">
         <v>66</v>
       </c>
-      <c r="L21" s="22" t="n">
+      <c r="M21" s="21" t="n">
         <v>105</v>
       </c>
     </row>
@@ -20768,31 +20884,36 @@
           <t>―</t>
         </is>
       </c>
-      <c r="D22" s="25" t="n">
+      <c r="D22" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="n">
         <v>9147</v>
       </c>
-      <c r="E22" s="25" t="n">
+      <c r="F22" s="25" t="n">
         <v>9179</v>
       </c>
-      <c r="F22" s="25" t="n">
+      <c r="G22" s="25" t="n">
         <v>9213</v>
       </c>
-      <c r="G22" s="25" t="n">
+      <c r="H22" s="25" t="n">
         <v>9211</v>
       </c>
-      <c r="H22" s="25" t="n">
+      <c r="I22" s="25" t="n">
         <v>9250</v>
       </c>
-      <c r="I22" s="25" t="n">
+      <c r="J22" s="25" t="n">
         <v>9491</v>
       </c>
-      <c r="J22" s="25" t="n">
+      <c r="K22" s="25" t="n">
         <v>9395</v>
       </c>
-      <c r="K22" s="25" t="n">
+      <c r="L22" s="25" t="n">
         <v>9127</v>
       </c>
-      <c r="L22" s="25" t="n">
+      <c r="M22" s="25" t="n">
         <v>9090</v>
       </c>
     </row>
@@ -20808,43 +20929,49 @@
           <t>―</t>
         </is>
       </c>
-      <c r="D23" s="28" t="n">
+      <c r="D23" s="28" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E23" s="29" t="n">
         <v>9068</v>
       </c>
-      <c r="E23" s="28" t="n">
+      <c r="F23" s="29" t="n">
         <v>9099.1</v>
       </c>
-      <c r="F23" s="28" t="n">
+      <c r="G23" s="29" t="n">
         <v>9131.700000000001</v>
       </c>
-      <c r="G23" s="28" t="n">
+      <c r="H23" s="29" t="n">
         <v>9129.5</v>
       </c>
-      <c r="H23" s="28" t="n">
+      <c r="I23" s="29" t="n">
         <v>9169.6</v>
       </c>
-      <c r="I23" s="28" t="n">
+      <c r="J23" s="29" t="n">
         <v>9409.1</v>
       </c>
-      <c r="J23" s="28" t="n">
+      <c r="K23" s="29" t="n">
         <v>9314.799999999999</v>
       </c>
-      <c r="K23" s="28" t="n">
+      <c r="L23" s="29" t="n">
         <v>9049</v>
       </c>
-      <c r="L23" s="29" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="104" customHeight="1">
+      <c r="M23" s="28" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="150" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>注1）本表の値は必要資料が未受領であることによる暫定値です。確定値ではありません。
-注2）第1段階から第3段階は公費軽減の対象です。乗率は公費軽減前の値であり、補正後被保険者数はこの乗率で算定します（公費軽減分は国・都道府県・市町村の公費で補填されます）。保険料収入と低所得者軽減公費を別々に置く様式では、この乗率で計算した収入に軽減公費を重ねて加えないでください。
-注3）構成比は令和6年度の実績で固定しています。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数からシステムが算定する補正後被保険者数は当方の値と一致します。令和7年度の構成比に改めると係数は1.015890となり、算定上の月額が163円下がります。これは構成比の作り方ではなく係数の選択そのものです。
-注4）第10期の段階数・乗率は政令改正により変わり得ます（確認事項No.33）。本表は第9期の16段階・乗率による暫定の値です。</t>
+注2）割合は公費軽減前の値です。第1段階から第3段階は公費軽減の対象ですが、補正後被保険者数はこの割合で算定します（公費軽減分は国・都道府県・市町村の公費で補填されます）。見える化システムが「①標準段階区分・割合」の画面に表示する0.4550・0.6850・0.6900…も公費軽減前の値であり、基準がそろっています。保険料収入と低所得者軽減公費を別々に置く様式では、この割合で計算した収入に軽減公費を重ねて加えないでください。
+注3）基準所得金額は第7段階から第16段階の10件です。第1段階から第6段階は本人の合計所得金額の下限による区分ではないため（生活保護受給・世帯の課税状況・合計所得金額＋課税年金収入額による）基準所得金額を持ちません。画面も当該欄は入力を受け付けません。第7段階から第13段階の額は、画面が標準として表示している1,200,000円から7,200,000円と一致します。
+注4）構成比は令和6年度の実績で固定しています。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数からシステムが算定する補正後被保険者数は当方の値と一致します。令和7年度の構成比に改めると係数は1.015890となり、算定上の月額が163円下がります。これは構成比の作り方ではなく係数の選択そのものです。
+注5）第10期の段階数・割合・基準所得金額は政令改正により変わり得ます（確認事項No.33）。本表は第9期の条例の16段階・割合による暫定の値です。令和8年3月の全国課長会議資料は、保険料段階の基準額を80.9万円から82.65万円に改める政令改正が済んでおり、条例改正の手続を要するとしています。</t>
         </is>
       </c>
     </row>
@@ -20870,47 +20997,47 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
+          <t>基準所得金額（円）</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
           <t>令和9年度</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>令和10年度</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>令和11年度</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>令和12年度</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>令和17年度</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>令和22年度</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>令和27年度</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>令和32年度</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>基準所得金額</t>
         </is>
       </c>
     </row>
@@ -20926,34 +21053,34 @@
       <c r="C28" s="15" t="n">
         <v>0.455</v>
       </c>
-      <c r="D28" s="21" t="n">
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="n">
         <v>1462</v>
       </c>
-      <c r="E28" s="21" t="n">
+      <c r="F28" s="22" t="n">
         <v>1467</v>
       </c>
-      <c r="F28" s="21" t="n">
+      <c r="G28" s="22" t="n">
         <v>1473</v>
       </c>
-      <c r="G28" s="21" t="n">
+      <c r="H28" s="22" t="n">
         <v>1473</v>
       </c>
-      <c r="H28" s="21" t="n">
+      <c r="I28" s="22" t="n">
         <v>1479</v>
       </c>
-      <c r="I28" s="21" t="n">
+      <c r="J28" s="22" t="n">
         <v>1517</v>
       </c>
-      <c r="J28" s="21" t="n">
+      <c r="K28" s="22" t="n">
         <v>1502</v>
       </c>
-      <c r="K28" s="21" t="n">
+      <c r="L28" s="22" t="n">
         <v>1459</v>
-      </c>
-      <c r="L28" s="22" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -20968,34 +21095,34 @@
       <c r="C29" s="15" t="n">
         <v>0.6850000000000001</v>
       </c>
-      <c r="D29" s="21" t="n">
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="n">
         <v>1178</v>
       </c>
-      <c r="E29" s="21" t="n">
+      <c r="F29" s="22" t="n">
         <v>1182</v>
       </c>
-      <c r="F29" s="21" t="n">
+      <c r="G29" s="22" t="n">
         <v>1186</v>
       </c>
-      <c r="G29" s="21" t="n">
+      <c r="H29" s="22" t="n">
         <v>1186</v>
       </c>
-      <c r="H29" s="21" t="n">
+      <c r="I29" s="22" t="n">
         <v>1191</v>
       </c>
-      <c r="I29" s="21" t="n">
+      <c r="J29" s="22" t="n">
         <v>1222</v>
       </c>
-      <c r="J29" s="21" t="n">
+      <c r="K29" s="22" t="n">
         <v>1209</v>
       </c>
-      <c r="K29" s="21" t="n">
+      <c r="L29" s="22" t="n">
         <v>1175</v>
-      </c>
-      <c r="L29" s="22" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -21010,34 +21137,34 @@
       <c r="C30" s="15" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="D30" s="21" t="n">
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="n">
         <v>937</v>
       </c>
-      <c r="E30" s="21" t="n">
+      <c r="F30" s="22" t="n">
         <v>940</v>
       </c>
-      <c r="F30" s="21" t="n">
+      <c r="G30" s="22" t="n">
         <v>944</v>
       </c>
-      <c r="G30" s="21" t="n">
+      <c r="H30" s="22" t="n">
         <v>943</v>
       </c>
-      <c r="H30" s="21" t="n">
+      <c r="I30" s="22" t="n">
         <v>947</v>
       </c>
-      <c r="I30" s="21" t="n">
+      <c r="J30" s="22" t="n">
         <v>972</v>
       </c>
-      <c r="J30" s="21" t="n">
+      <c r="K30" s="22" t="n">
         <v>962</v>
       </c>
-      <c r="K30" s="21" t="n">
+      <c r="L30" s="22" t="n">
         <v>935</v>
-      </c>
-      <c r="L30" s="22" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -21052,34 +21179,34 @@
       <c r="C31" s="15" t="n">
         <v>0.9</v>
       </c>
-      <c r="D31" s="21" t="n">
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="n">
         <v>753</v>
       </c>
-      <c r="E31" s="21" t="n">
+      <c r="F31" s="22" t="n">
         <v>756</v>
       </c>
-      <c r="F31" s="21" t="n">
+      <c r="G31" s="22" t="n">
         <v>759</v>
       </c>
-      <c r="G31" s="21" t="n">
+      <c r="H31" s="22" t="n">
         <v>758</v>
       </c>
-      <c r="H31" s="21" t="n">
+      <c r="I31" s="22" t="n">
         <v>762</v>
       </c>
-      <c r="I31" s="21" t="n">
+      <c r="J31" s="22" t="n">
         <v>782</v>
       </c>
-      <c r="J31" s="21" t="n">
+      <c r="K31" s="22" t="n">
         <v>773</v>
       </c>
-      <c r="K31" s="21" t="n">
+      <c r="L31" s="22" t="n">
         <v>751</v>
-      </c>
-      <c r="L31" s="22" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -21094,34 +21221,34 @@
       <c r="C32" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="21" t="n">
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="n">
         <v>1185</v>
       </c>
-      <c r="E32" s="21" t="n">
+      <c r="F32" s="22" t="n">
         <v>1189</v>
       </c>
-      <c r="F32" s="21" t="n">
+      <c r="G32" s="22" t="n">
         <v>1193</v>
       </c>
-      <c r="G32" s="21" t="n">
+      <c r="H32" s="22" t="n">
         <v>1193</v>
       </c>
-      <c r="H32" s="21" t="n">
+      <c r="I32" s="22" t="n">
         <v>1198</v>
       </c>
-      <c r="I32" s="21" t="n">
+      <c r="J32" s="22" t="n">
         <v>1229</v>
       </c>
-      <c r="J32" s="21" t="n">
+      <c r="K32" s="22" t="n">
         <v>1217</v>
       </c>
-      <c r="K32" s="21" t="n">
+      <c r="L32" s="22" t="n">
         <v>1182</v>
-      </c>
-      <c r="L32" s="22" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -21136,34 +21263,34 @@
       <c r="C33" s="15" t="n">
         <v>1.2</v>
       </c>
-      <c r="D33" s="21" t="n">
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="n">
         <v>1382</v>
       </c>
-      <c r="E33" s="21" t="n">
+      <c r="F33" s="22" t="n">
         <v>1387</v>
       </c>
-      <c r="F33" s="21" t="n">
+      <c r="G33" s="22" t="n">
         <v>1392</v>
       </c>
-      <c r="G33" s="21" t="n">
+      <c r="H33" s="22" t="n">
         <v>1392</v>
       </c>
-      <c r="H33" s="21" t="n">
+      <c r="I33" s="22" t="n">
         <v>1398</v>
       </c>
-      <c r="I33" s="21" t="n">
+      <c r="J33" s="22" t="n">
         <v>1434</v>
       </c>
-      <c r="J33" s="21" t="n">
+      <c r="K33" s="22" t="n">
         <v>1420</v>
       </c>
-      <c r="K33" s="21" t="n">
+      <c r="L33" s="22" t="n">
         <v>1379</v>
-      </c>
-      <c r="L33" s="22" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -21179,31 +21306,31 @@
         <v>1.3</v>
       </c>
       <c r="D34" s="21" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="E34" s="22" t="n">
         <v>1233</v>
       </c>
-      <c r="E34" s="21" t="n">
+      <c r="F34" s="22" t="n">
         <v>1238</v>
       </c>
-      <c r="F34" s="21" t="n">
+      <c r="G34" s="22" t="n">
         <v>1242</v>
       </c>
-      <c r="G34" s="21" t="n">
+      <c r="H34" s="22" t="n">
         <v>1242</v>
       </c>
-      <c r="H34" s="21" t="n">
+      <c r="I34" s="22" t="n">
         <v>1247</v>
       </c>
-      <c r="I34" s="21" t="n">
+      <c r="J34" s="22" t="n">
         <v>1280</v>
       </c>
-      <c r="J34" s="21" t="n">
+      <c r="K34" s="22" t="n">
         <v>1267</v>
       </c>
-      <c r="K34" s="21" t="n">
+      <c r="L34" s="22" t="n">
         <v>1231</v>
-      </c>
-      <c r="L34" s="22" t="n">
-        <v>1200000</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -21219,31 +21346,31 @@
         <v>1.5</v>
       </c>
       <c r="D35" s="21" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="E35" s="22" t="n">
         <v>527</v>
       </c>
-      <c r="E35" s="21" t="n">
+      <c r="F35" s="22" t="n">
         <v>529</v>
       </c>
-      <c r="F35" s="21" t="n">
+      <c r="G35" s="22" t="n">
         <v>531</v>
       </c>
-      <c r="G35" s="21" t="n">
+      <c r="H35" s="22" t="n">
         <v>531</v>
       </c>
-      <c r="H35" s="21" t="n">
+      <c r="I35" s="22" t="n">
         <v>533</v>
       </c>
-      <c r="I35" s="21" t="n">
+      <c r="J35" s="22" t="n">
         <v>547</v>
       </c>
-      <c r="J35" s="21" t="n">
+      <c r="K35" s="22" t="n">
         <v>542</v>
       </c>
-      <c r="K35" s="21" t="n">
+      <c r="L35" s="22" t="n">
         <v>526</v>
-      </c>
-      <c r="L35" s="22" t="n">
-        <v>2100000</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -21259,31 +21386,31 @@
         <v>1.7</v>
       </c>
       <c r="D36" s="21" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="E36" s="22" t="n">
         <v>203</v>
       </c>
-      <c r="E36" s="21" t="n">
+      <c r="F36" s="22" t="n">
         <v>204</v>
       </c>
-      <c r="F36" s="21" t="n">
+      <c r="G36" s="22" t="n">
         <v>204</v>
       </c>
-      <c r="G36" s="21" t="n">
+      <c r="H36" s="22" t="n">
         <v>204</v>
       </c>
-      <c r="H36" s="21" t="n">
+      <c r="I36" s="22" t="n">
         <v>205</v>
       </c>
-      <c r="I36" s="21" t="n">
+      <c r="J36" s="22" t="n">
         <v>210</v>
       </c>
-      <c r="J36" s="21" t="n">
+      <c r="K36" s="22" t="n">
         <v>208</v>
       </c>
-      <c r="K36" s="21" t="n">
+      <c r="L36" s="22" t="n">
         <v>202</v>
-      </c>
-      <c r="L36" s="22" t="n">
-        <v>3200000</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -21299,31 +21426,31 @@
         <v>1.9</v>
       </c>
       <c r="D37" s="21" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="E37" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="E37" s="21" t="n">
+      <c r="F37" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="F37" s="21" t="n">
+      <c r="G37" s="22" t="n">
         <v>101</v>
       </c>
-      <c r="G37" s="21" t="n">
+      <c r="H37" s="22" t="n">
         <v>101</v>
       </c>
-      <c r="H37" s="21" t="n">
+      <c r="I37" s="22" t="n">
         <v>101</v>
       </c>
-      <c r="I37" s="21" t="n">
+      <c r="J37" s="22" t="n">
         <v>104</v>
       </c>
-      <c r="J37" s="21" t="n">
+      <c r="K37" s="22" t="n">
         <v>103</v>
       </c>
-      <c r="K37" s="21" t="n">
+      <c r="L37" s="22" t="n">
         <v>100</v>
-      </c>
-      <c r="L37" s="22" t="n">
-        <v>4200000</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -21339,31 +21466,31 @@
         <v>2.1</v>
       </c>
       <c r="D38" s="21" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="E38" s="22" t="n">
         <v>54</v>
       </c>
-      <c r="E38" s="21" t="n">
+      <c r="F38" s="22" t="n">
         <v>54</v>
       </c>
-      <c r="F38" s="21" t="n">
+      <c r="G38" s="22" t="n">
         <v>54</v>
       </c>
-      <c r="G38" s="21" t="n">
+      <c r="H38" s="22" t="n">
         <v>54</v>
       </c>
-      <c r="H38" s="21" t="n">
+      <c r="I38" s="22" t="n">
         <v>55</v>
       </c>
-      <c r="I38" s="21" t="n">
+      <c r="J38" s="22" t="n">
         <v>56</v>
       </c>
-      <c r="J38" s="21" t="n">
+      <c r="K38" s="22" t="n">
         <v>55</v>
       </c>
-      <c r="K38" s="21" t="n">
+      <c r="L38" s="22" t="n">
         <v>54</v>
-      </c>
-      <c r="L38" s="22" t="n">
-        <v>5200000</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -21379,31 +21506,31 @@
         <v>2.3</v>
       </c>
       <c r="D39" s="21" t="n">
+        <v>6200000</v>
+      </c>
+      <c r="E39" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="E39" s="21" t="n">
+      <c r="F39" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="F39" s="21" t="n">
+      <c r="G39" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="G39" s="21" t="n">
+      <c r="H39" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="H39" s="21" t="n">
+      <c r="I39" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="I39" s="21" t="n">
+      <c r="J39" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="J39" s="21" t="n">
+      <c r="K39" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="K39" s="21" t="n">
+      <c r="L39" s="22" t="n">
         <v>24</v>
-      </c>
-      <c r="L39" s="22" t="n">
-        <v>6200000</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -21419,31 +21546,31 @@
         <v>2.4</v>
       </c>
       <c r="D40" s="21" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="E40" s="22" t="n">
         <v>109</v>
       </c>
-      <c r="E40" s="21" t="n">
+      <c r="F40" s="22" t="n">
         <v>109</v>
       </c>
-      <c r="F40" s="21" t="n">
+      <c r="G40" s="22" t="n">
         <v>110</v>
       </c>
-      <c r="G40" s="21" t="n">
+      <c r="H40" s="22" t="n">
         <v>110</v>
       </c>
-      <c r="H40" s="21" t="n">
+      <c r="I40" s="22" t="n">
         <v>110</v>
       </c>
-      <c r="I40" s="21" t="n">
+      <c r="J40" s="22" t="n">
         <v>113</v>
       </c>
-      <c r="J40" s="21" t="n">
+      <c r="K40" s="22" t="n">
         <v>112</v>
       </c>
-      <c r="K40" s="21" t="n">
+      <c r="L40" s="22" t="n">
         <v>109</v>
-      </c>
-      <c r="L40" s="22" t="n">
-        <v>7200000</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -21458,34 +21585,34 @@
           <t>―</t>
         </is>
       </c>
-      <c r="D41" s="25" t="n">
+      <c r="D41" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E41" s="25" t="n">
         <v>9147</v>
       </c>
-      <c r="E41" s="25" t="n">
+      <c r="F41" s="25" t="n">
         <v>9179</v>
       </c>
-      <c r="F41" s="25" t="n">
+      <c r="G41" s="25" t="n">
         <v>9213</v>
       </c>
-      <c r="G41" s="25" t="n">
+      <c r="H41" s="25" t="n">
         <v>9211</v>
       </c>
-      <c r="H41" s="25" t="n">
+      <c r="I41" s="25" t="n">
         <v>9250</v>
       </c>
-      <c r="I41" s="25" t="n">
+      <c r="J41" s="25" t="n">
         <v>9491</v>
       </c>
-      <c r="J41" s="25" t="n">
+      <c r="K41" s="25" t="n">
         <v>9395</v>
       </c>
-      <c r="K41" s="25" t="n">
+      <c r="L41" s="25" t="n">
         <v>9127</v>
-      </c>
-      <c r="L41" s="25" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -21500,34 +21627,34 @@
           <t>―</t>
         </is>
       </c>
-      <c r="D42" s="31" t="n">
+      <c r="D42" s="31" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E42" s="32" t="n">
         <v>8998.5</v>
       </c>
-      <c r="E42" s="31" t="n">
+      <c r="F42" s="32" t="n">
         <v>9029.5</v>
       </c>
-      <c r="F42" s="31" t="n">
+      <c r="G42" s="32" t="n">
         <v>9062.9</v>
       </c>
-      <c r="G42" s="31" t="n">
+      <c r="H42" s="32" t="n">
         <v>9061.299999999999</v>
       </c>
-      <c r="H42" s="31" t="n">
+      <c r="I42" s="32" t="n">
         <v>9099.299999999999</v>
       </c>
-      <c r="I42" s="31" t="n">
+      <c r="J42" s="32" t="n">
         <v>9337</v>
       </c>
-      <c r="J42" s="31" t="n">
+      <c r="K42" s="32" t="n">
         <v>9243.299999999999</v>
       </c>
-      <c r="K42" s="31" t="n">
+      <c r="L42" s="32" t="n">
         <v>8979.5</v>
-      </c>
-      <c r="L42" s="32" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
       </c>
     </row>
     <row r="43" ht="118" customHeight="1">
@@ -21562,47 +21689,47 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
+          <t>基準所得金額（円）</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
           <t>令和9年度</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>令和10年度</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>令和11年度</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>令和12年度</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="I46" s="5" t="inlineStr">
         <is>
           <t>令和17年度</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="J46" s="5" t="inlineStr">
         <is>
           <t>令和22年度</t>
         </is>
       </c>
-      <c r="J46" s="5" t="inlineStr">
+      <c r="K46" s="5" t="inlineStr">
         <is>
           <t>令和27年度</t>
         </is>
       </c>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="L46" s="5" t="inlineStr">
         <is>
           <t>令和32年度</t>
-        </is>
-      </c>
-      <c r="L46" s="5" t="inlineStr">
-        <is>
-          <t>基準所得金額</t>
         </is>
       </c>
     </row>
@@ -21618,34 +21745,34 @@
       <c r="C47" s="15" t="n">
         <v>0.455</v>
       </c>
-      <c r="D47" s="21" t="n">
+      <c r="D47" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E47" s="22" t="n">
         <v>1457</v>
       </c>
-      <c r="E47" s="21" t="n">
+      <c r="F47" s="22" t="n">
         <v>1456</v>
       </c>
-      <c r="F47" s="21" t="n">
+      <c r="G47" s="22" t="n">
         <v>1456</v>
       </c>
-      <c r="G47" s="21" t="n">
+      <c r="H47" s="22" t="n">
         <v>1456</v>
       </c>
-      <c r="H47" s="21" t="n">
+      <c r="I47" s="22" t="n">
         <v>1465</v>
       </c>
-      <c r="I47" s="21" t="n">
+      <c r="J47" s="22" t="n">
         <v>1499</v>
       </c>
-      <c r="J47" s="21" t="n">
+      <c r="K47" s="22" t="n">
         <v>1482</v>
       </c>
-      <c r="K47" s="21" t="n">
+      <c r="L47" s="22" t="n">
         <v>1438</v>
-      </c>
-      <c r="L47" s="22" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -21660,34 +21787,34 @@
       <c r="C48" s="15" t="n">
         <v>0.6850000000000001</v>
       </c>
-      <c r="D48" s="21" t="n">
+      <c r="D48" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E48" s="22" t="n">
         <v>1174</v>
       </c>
-      <c r="E48" s="21" t="n">
+      <c r="F48" s="22" t="n">
         <v>1173</v>
       </c>
-      <c r="F48" s="21" t="n">
+      <c r="G48" s="22" t="n">
         <v>1172</v>
       </c>
-      <c r="G48" s="21" t="n">
+      <c r="H48" s="22" t="n">
         <v>1172</v>
       </c>
-      <c r="H48" s="21" t="n">
+      <c r="I48" s="22" t="n">
         <v>1180</v>
       </c>
-      <c r="I48" s="21" t="n">
+      <c r="J48" s="22" t="n">
         <v>1207</v>
       </c>
-      <c r="J48" s="21" t="n">
+      <c r="K48" s="22" t="n">
         <v>1193</v>
       </c>
-      <c r="K48" s="21" t="n">
+      <c r="L48" s="22" t="n">
         <v>1158</v>
-      </c>
-      <c r="L48" s="22" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -21702,34 +21829,34 @@
       <c r="C49" s="15" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="D49" s="21" t="n">
+      <c r="D49" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E49" s="22" t="n">
         <v>934</v>
       </c>
-      <c r="E49" s="21" t="n">
+      <c r="F49" s="22" t="n">
         <v>933</v>
       </c>
-      <c r="F49" s="21" t="n">
+      <c r="G49" s="22" t="n">
         <v>933</v>
       </c>
-      <c r="G49" s="21" t="n">
+      <c r="H49" s="22" t="n">
         <v>933</v>
       </c>
-      <c r="H49" s="21" t="n">
+      <c r="I49" s="22" t="n">
         <v>939</v>
       </c>
-      <c r="I49" s="21" t="n">
+      <c r="J49" s="22" t="n">
         <v>960</v>
       </c>
-      <c r="J49" s="21" t="n">
+      <c r="K49" s="22" t="n">
         <v>950</v>
       </c>
-      <c r="K49" s="21" t="n">
+      <c r="L49" s="22" t="n">
         <v>921</v>
-      </c>
-      <c r="L49" s="22" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -21744,34 +21871,34 @@
       <c r="C50" s="15" t="n">
         <v>0.9</v>
       </c>
-      <c r="D50" s="21" t="n">
+      <c r="D50" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E50" s="22" t="n">
         <v>750</v>
       </c>
-      <c r="E50" s="21" t="n">
+      <c r="F50" s="22" t="n">
         <v>750</v>
       </c>
-      <c r="F50" s="21" t="n">
+      <c r="G50" s="22" t="n">
         <v>750</v>
       </c>
-      <c r="G50" s="21" t="n">
+      <c r="H50" s="22" t="n">
         <v>750</v>
       </c>
-      <c r="H50" s="21" t="n">
+      <c r="I50" s="22" t="n">
         <v>755</v>
       </c>
-      <c r="I50" s="21" t="n">
+      <c r="J50" s="22" t="n">
         <v>772</v>
       </c>
-      <c r="J50" s="21" t="n">
+      <c r="K50" s="22" t="n">
         <v>763</v>
       </c>
-      <c r="K50" s="21" t="n">
+      <c r="L50" s="22" t="n">
         <v>740</v>
-      </c>
-      <c r="L50" s="22" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -21786,34 +21913,34 @@
       <c r="C51" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D51" s="21" t="n">
+      <c r="D51" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E51" s="22" t="n">
         <v>1181</v>
       </c>
-      <c r="E51" s="21" t="n">
+      <c r="F51" s="22" t="n">
         <v>1180</v>
       </c>
-      <c r="F51" s="21" t="n">
+      <c r="G51" s="22" t="n">
         <v>1179</v>
       </c>
-      <c r="G51" s="21" t="n">
+      <c r="H51" s="22" t="n">
         <v>1179</v>
       </c>
-      <c r="H51" s="21" t="n">
+      <c r="I51" s="22" t="n">
         <v>1187</v>
       </c>
-      <c r="I51" s="21" t="n">
+      <c r="J51" s="22" t="n">
         <v>1214</v>
       </c>
-      <c r="J51" s="21" t="n">
+      <c r="K51" s="22" t="n">
         <v>1201</v>
       </c>
-      <c r="K51" s="21" t="n">
+      <c r="L51" s="22" t="n">
         <v>1165</v>
-      </c>
-      <c r="L51" s="22" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -21828,34 +21955,34 @@
       <c r="C52" s="15" t="n">
         <v>1.2</v>
       </c>
-      <c r="D52" s="21" t="n">
+      <c r="D52" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E52" s="22" t="n">
         <v>1378</v>
       </c>
-      <c r="E52" s="21" t="n">
+      <c r="F52" s="22" t="n">
         <v>1377</v>
       </c>
-      <c r="F52" s="21" t="n">
+      <c r="G52" s="22" t="n">
         <v>1376</v>
       </c>
-      <c r="G52" s="21" t="n">
+      <c r="H52" s="22" t="n">
         <v>1376</v>
       </c>
-      <c r="H52" s="21" t="n">
+      <c r="I52" s="22" t="n">
         <v>1385</v>
       </c>
-      <c r="I52" s="21" t="n">
+      <c r="J52" s="22" t="n">
         <v>1417</v>
       </c>
-      <c r="J52" s="21" t="n">
+      <c r="K52" s="22" t="n">
         <v>1401</v>
       </c>
-      <c r="K52" s="21" t="n">
+      <c r="L52" s="22" t="n">
         <v>1359</v>
-      </c>
-      <c r="L52" s="22" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -21871,31 +21998,31 @@
         <v>1.3</v>
       </c>
       <c r="D53" s="21" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="E53" s="22" t="n">
         <v>1229</v>
       </c>
-      <c r="E53" s="21" t="n">
+      <c r="F53" s="22" t="n">
         <v>1229</v>
       </c>
-      <c r="F53" s="21" t="n">
+      <c r="G53" s="22" t="n">
         <v>1228</v>
       </c>
-      <c r="G53" s="21" t="n">
+      <c r="H53" s="22" t="n">
         <v>1228</v>
       </c>
-      <c r="H53" s="21" t="n">
+      <c r="I53" s="22" t="n">
         <v>1236</v>
       </c>
-      <c r="I53" s="21" t="n">
+      <c r="J53" s="22" t="n">
         <v>1264</v>
       </c>
-      <c r="J53" s="21" t="n">
+      <c r="K53" s="22" t="n">
         <v>1250</v>
       </c>
-      <c r="K53" s="21" t="n">
+      <c r="L53" s="22" t="n">
         <v>1213</v>
-      </c>
-      <c r="L53" s="22" t="n">
-        <v>1200000</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -21911,31 +22038,31 @@
         <v>1.5</v>
       </c>
       <c r="D54" s="21" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="E54" s="22" t="n">
         <v>526</v>
       </c>
-      <c r="E54" s="21" t="n">
+      <c r="F54" s="22" t="n">
         <v>525</v>
       </c>
-      <c r="F54" s="21" t="n">
+      <c r="G54" s="22" t="n">
         <v>525</v>
       </c>
-      <c r="G54" s="21" t="n">
+      <c r="H54" s="22" t="n">
         <v>525</v>
       </c>
-      <c r="H54" s="21" t="n">
+      <c r="I54" s="22" t="n">
         <v>529</v>
       </c>
-      <c r="I54" s="21" t="n">
+      <c r="J54" s="22" t="n">
         <v>540</v>
       </c>
-      <c r="J54" s="21" t="n">
+      <c r="K54" s="22" t="n">
         <v>534</v>
       </c>
-      <c r="K54" s="21" t="n">
+      <c r="L54" s="22" t="n">
         <v>518</v>
-      </c>
-      <c r="L54" s="22" t="n">
-        <v>2100000</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -21951,31 +22078,31 @@
         <v>1.7</v>
       </c>
       <c r="D55" s="21" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="E55" s="22" t="n">
         <v>202</v>
       </c>
-      <c r="E55" s="21" t="n">
+      <c r="F55" s="22" t="n">
         <v>202</v>
       </c>
-      <c r="F55" s="21" t="n">
+      <c r="G55" s="22" t="n">
         <v>202</v>
       </c>
-      <c r="G55" s="21" t="n">
+      <c r="H55" s="22" t="n">
         <v>202</v>
       </c>
-      <c r="H55" s="21" t="n">
+      <c r="I55" s="22" t="n">
         <v>203</v>
       </c>
-      <c r="I55" s="21" t="n">
+      <c r="J55" s="22" t="n">
         <v>208</v>
       </c>
-      <c r="J55" s="21" t="n">
+      <c r="K55" s="22" t="n">
         <v>206</v>
       </c>
-      <c r="K55" s="21" t="n">
+      <c r="L55" s="22" t="n">
         <v>199</v>
-      </c>
-      <c r="L55" s="22" t="n">
-        <v>3200000</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -21991,31 +22118,31 @@
         <v>1.9</v>
       </c>
       <c r="D56" s="21" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="E56" s="22" t="n">
         <v>99</v>
       </c>
-      <c r="E56" s="21" t="n">
+      <c r="F56" s="22" t="n">
         <v>99</v>
       </c>
-      <c r="F56" s="21" t="n">
+      <c r="G56" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="G56" s="21" t="n">
+      <c r="H56" s="22" t="n">
         <v>99</v>
       </c>
-      <c r="H56" s="21" t="n">
+      <c r="I56" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="I56" s="21" t="n">
+      <c r="J56" s="22" t="n">
         <v>102</v>
       </c>
-      <c r="J56" s="21" t="n">
+      <c r="K56" s="22" t="n">
         <v>101</v>
       </c>
-      <c r="K56" s="21" t="n">
+      <c r="L56" s="22" t="n">
         <v>98</v>
-      </c>
-      <c r="L56" s="22" t="n">
-        <v>4200000</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -22031,31 +22158,31 @@
         <v>2.1</v>
       </c>
       <c r="D57" s="21" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="E57" s="22" t="n">
         <v>54</v>
       </c>
-      <c r="E57" s="21" t="n">
+      <c r="F57" s="22" t="n">
         <v>54</v>
       </c>
-      <c r="F57" s="21" t="n">
+      <c r="G57" s="22" t="n">
         <v>54</v>
       </c>
-      <c r="G57" s="21" t="n">
+      <c r="H57" s="22" t="n">
         <v>54</v>
       </c>
-      <c r="H57" s="21" t="n">
+      <c r="I57" s="22" t="n">
         <v>54</v>
       </c>
-      <c r="I57" s="21" t="n">
+      <c r="J57" s="22" t="n">
         <v>55</v>
       </c>
-      <c r="J57" s="21" t="n">
+      <c r="K57" s="22" t="n">
         <v>55</v>
       </c>
-      <c r="K57" s="21" t="n">
+      <c r="L57" s="22" t="n">
         <v>53</v>
-      </c>
-      <c r="L57" s="22" t="n">
-        <v>5200000</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -22071,31 +22198,31 @@
         <v>2.3</v>
       </c>
       <c r="D58" s="21" t="n">
+        <v>6200000</v>
+      </c>
+      <c r="E58" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="E58" s="21" t="n">
+      <c r="F58" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="F58" s="21" t="n">
+      <c r="G58" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="G58" s="21" t="n">
+      <c r="H58" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="H58" s="21" t="n">
+      <c r="I58" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="I58" s="21" t="n">
+      <c r="J58" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="J58" s="21" t="n">
+      <c r="K58" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="K58" s="21" t="n">
+      <c r="L58" s="22" t="n">
         <v>24</v>
-      </c>
-      <c r="L58" s="22" t="n">
-        <v>6200000</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -22111,31 +22238,31 @@
         <v>2.4</v>
       </c>
       <c r="D59" s="21" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="E59" s="22" t="n">
         <v>108</v>
       </c>
-      <c r="E59" s="21" t="n">
+      <c r="F59" s="22" t="n">
         <v>108</v>
       </c>
-      <c r="F59" s="21" t="n">
+      <c r="G59" s="22" t="n">
         <v>108</v>
       </c>
-      <c r="G59" s="21" t="n">
+      <c r="H59" s="22" t="n">
         <v>108</v>
       </c>
-      <c r="H59" s="21" t="n">
+      <c r="I59" s="22" t="n">
         <v>109</v>
       </c>
-      <c r="I59" s="21" t="n">
+      <c r="J59" s="22" t="n">
         <v>112</v>
       </c>
-      <c r="J59" s="21" t="n">
+      <c r="K59" s="22" t="n">
         <v>110</v>
       </c>
-      <c r="K59" s="21" t="n">
+      <c r="L59" s="22" t="n">
         <v>107</v>
-      </c>
-      <c r="L59" s="22" t="n">
-        <v>7200000</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -22150,34 +22277,34 @@
           <t>―</t>
         </is>
       </c>
-      <c r="D60" s="25" t="n">
+      <c r="D60" s="25" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E60" s="25" t="n">
         <v>9116</v>
       </c>
-      <c r="E60" s="25" t="n">
+      <c r="F60" s="25" t="n">
         <v>9110</v>
       </c>
-      <c r="F60" s="25" t="n">
+      <c r="G60" s="25" t="n">
         <v>9107</v>
       </c>
-      <c r="G60" s="25" t="n">
+      <c r="H60" s="25" t="n">
         <v>9106</v>
       </c>
-      <c r="H60" s="25" t="n">
+      <c r="I60" s="25" t="n">
         <v>9166</v>
       </c>
-      <c r="I60" s="25" t="n">
+      <c r="J60" s="25" t="n">
         <v>9375</v>
       </c>
-      <c r="J60" s="25" t="n">
+      <c r="K60" s="25" t="n">
         <v>9270</v>
       </c>
-      <c r="K60" s="25" t="n">
+      <c r="L60" s="25" t="n">
         <v>8993</v>
-      </c>
-      <c r="L60" s="25" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -22192,34 +22319,34 @@
           <t>―</t>
         </is>
       </c>
-      <c r="D61" s="33" t="n">
+      <c r="D61" s="31" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E61" s="33" t="n">
         <v>31</v>
       </c>
-      <c r="E61" s="33" t="n">
+      <c r="F61" s="33" t="n">
         <v>69</v>
       </c>
-      <c r="F61" s="33" t="n">
+      <c r="G61" s="33" t="n">
         <v>106</v>
       </c>
-      <c r="G61" s="33" t="n">
+      <c r="H61" s="33" t="n">
         <v>105</v>
       </c>
-      <c r="H61" s="33" t="n">
+      <c r="I61" s="33" t="n">
         <v>84</v>
       </c>
-      <c r="I61" s="33" t="n">
+      <c r="J61" s="33" t="n">
         <v>116</v>
       </c>
-      <c r="J61" s="33" t="n">
+      <c r="K61" s="33" t="n">
         <v>125</v>
       </c>
-      <c r="K61" s="33" t="n">
+      <c r="L61" s="33" t="n">
         <v>134</v>
-      </c>
-      <c r="L61" s="32" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
       </c>
     </row>
     <row r="62" ht="90" customHeight="1">
@@ -22235,12 +22362,12 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:M1"/>
     <mergeCell ref="A43:L43"/>
-    <mergeCell ref="A1:L1"/>
     <mergeCell ref="A45:L45"/>
-    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="A24:M24"/>
+    <mergeCell ref="A2:M2"/>
     <mergeCell ref="A62:L62"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
+++ b/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
@@ -2554,7 +2554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3011,12 +3011,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>利用回（日）数も列の有無が利用者数とそろっていること</t>
+          <t>利用回（日）数の列の有無が利用者数とそろっていること</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>実績がなく1人1月あたりを出せない欄は0（「―」にしない）</t>
+          <t>画面に列のない要支援の欄を「―」にする</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -3032,21 +3032,21 @@
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="6" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>書き出した表の内訳の和と「計」の欄が一致すること</t>
+          <t>要介護度別の1人1月あたりを加重平均すると群の値に戻ること</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>02・03・04・05シートの全行を読み直して検算</t>
+          <t>総括表詳細（３）と一致する群の値に戻るか</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>378行を検算／合わない なし</t>
+          <t>食い違い0件</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -3057,21 +3057,21 @@
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>画面の第1号被保険者数に合わせる表の計が画面の値と一致すること</t>
+          <t>書き出した表の内訳の和と「計」の欄が一致すること</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>08シート3の各年度で Σ段階別 ＝ 画面の第1号被保険者数</t>
+          <t>02・03・04シートの全行を読み直して検算</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>全8年度（令和9年度・令和10年度・令和11年度・令和12年度・令和17年度・令和22年度・令和27年度・令和32年度）／合わない なし</t>
+          <t>270行を検算／合わない なし</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
@@ -3082,21 +3082,21 @@
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="6" t="n">
-        <v>20</v>
+        <v>18.3</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>画面の写しの年度が算定の年度と過不足なく一致すること</t>
+          <t>利用回（日）数の表に合計の列を置いていないこと</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>GAMEN13_HIHO のキー ＝ 令和9〜12・17・22・27・32年度</t>
+          <t>画面に合計の列がない（見出しと値の行の両方を見る）</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>画面の写し8年度／算定8年度</t>
+          <t>見出し11列（サービス（プルダウンで選ぶ）・単位・年度・要支援1・要支援2・要介護1・要介護2・要介護3・要介護4・要介護5）／見出しより右に値のある行 なし</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -3107,21 +3107,21 @@
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>21</v>
+        <v>18.6</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>基準所得金額が第7段階から第16段階の10件で昇順であること</t>
+          <t>令和7年度の1人1月あたりが画面の表示値と一致すること</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第1〜6段階は None（画面も入力欄なし）／第7段階以降は金額かつ昇順</t>
+          <t>画面の写し（訪問介護・訪問看護）と当方の年報による算定</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>欄なし 第1・2・3・4・5・6段階／金額10件（1,200,000〜10,200,000円）</t>
+          <t>2区分・12欄／合わない なし</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
@@ -3132,50 +3132,125 @@
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>画面の第1号被保険者数に合わせる表の計が画面の値と一致すること</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>08シート3の各年度で Σ段階別 ＝ 画面の第1号被保険者数</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>全8年度（令和9年度・令和10年度・令和11年度・令和12年度・令和17年度・令和22年度・令和27年度・令和32年度）／合わない なし</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>画面の写しの年度が算定の年度と過不足なく一致すること</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>GAMEN13_HIHO のキー ＝ 令和9〜12・17・22・27・32年度</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>画面の写し8年度／算定8年度</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>基準所得金額が第7段階から第16段階の10件で昇順であること</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>第1〜6段階は None（画面も入力欄なし）／第7段階以降は金額かつ昇順</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>欄なし 第1・2・3・4・5・6段階／金額10件（1,200,000〜10,200,000円）</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>第7段階から第13段階の基準所得金額が画面の標準の額と一致すること</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>STAGE から求めた額 ＝ 「①標準段階区分・割合」の画面が表示する額</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>1,200,000・2,100,000・3,200,000・4,200,000・5,200,000・6,200,000・7,200,000／画面 一致</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="9" t="inlineStr"/>
-      <c r="B27" s="9" t="inlineStr">
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="9" t="inlineStr"/>
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>自己点検の結果</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr"/>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>適合22件・不適合0件</t>
-        </is>
-      </c>
-      <c r="E27" s="26" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr"/>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>適合25件・不適合0件</t>
+        </is>
+      </c>
+      <c r="E30" s="26" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>注）本シートは点検の記録であり、本表の値が暫定値であることを変えるものではありません。点検しているのは内的整合であって、未受領の資料により値が動くことは点検では解消しません。</t>
         </is>
@@ -3183,9 +3258,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A28:E28"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A31:E31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
@@ -3334,7 +3409,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1">
+    <row r="9" ht="44" customHeight="1">
       <c r="A9" s="15" t="n">
         <v>4</v>
       </c>
@@ -3345,17 +3420,17 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>1月当たりの延べ回（日）数として掲げていた</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>同じ</t>
-        </is>
-      </c>
-      <c r="E9" s="34" t="inlineStr">
-        <is>
-          <t>変わらない</t>
+          <t>1人1月あたりに改めた（画面の写しによる。値の性質が変わったもので、延べに戻せば9月18日版と同じ）</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>掲げ方を改めた</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3839,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="36" customHeight="1">
+    <row r="33" ht="44" customHeight="1">
       <c r="A33" s="15" t="n">
         <v>1</v>
       </c>
@@ -3785,14 +3860,14 @@
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>内訳（要介護2 8.2）と合わないため8.2が正しい</t>
+          <t>内訳（要介護2 8.2）と合わないため8.2が正しかった。この欄は現在の版にありません（画面に合計の列がないため置いていません）</t>
         </is>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>注）ほかの全ての欄はお手元の版と当方の9月18日版で一致しています。本表では内訳と計が全ての行で一致することを自己点検で確かめています。</t>
+          <t>注）ほかの全ての欄はお手元の版と当方の9月18日版で一致しています。02・03・04シートは内訳と計が全ての行で一致することを自己点検で確かめています。</t>
         </is>
       </c>
     </row>
@@ -15136,7 +15211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L114"/>
+  <dimension ref="A1:K114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -15150,7 +15225,6 @@
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -15163,7 +15237,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>本表の値は必要資料が未受領であることによる暫定値です。確定値ではありません。　「施策反映　在宅サービス利用者数等」の画面に入れる利用回（日）数（回・日／月）です。利用回（日）数の欄は小数第1位まで受け付けます（確認事項No.135）。1人1月あたり回（日）数を令和7年度で固定し、利用者数に乗じています。</t>
+          <t>本表の値は必要資料が未受領であることによる暫定値です。確定値ではありません。　「施策反映　在宅サービス利用者数等」の画面から開く利用回（日）数の画面に入れる値です。入れるのは1人1月あたりの回（日）数であり、1月当たりの延べ回（日）数ではありません（令和8年9月30日に画面の写しで確かめました）。画面に合計の列はありません。欄は小数第1位まで受け付けます（確認事項No.135）。</t>
         </is>
       </c>
     </row>
@@ -15171,7 +15245,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>利用回（日）数（回・日／月・小数第1位）</t>
+          <t>1人1月あたりの利用回（日）数（回・日／月・小数第1位）</t>
         </is>
       </c>
     </row>
@@ -15179,7 +15253,7 @@
       <c r="A5" s="5" t="inlineStr"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>サービス</t>
+          <t>サービス（プルダウンで選ぶ）</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -15225,11 +15299,6 @@
       <c r="K5" s="5" t="inlineStr">
         <is>
           <t>要介護5</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>計</t>
         </is>
       </c>
     </row>
@@ -15264,22 +15333,19 @@
         </is>
       </c>
       <c r="G6" s="18" t="n">
-        <v>5536.3</v>
+        <v>23.6</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>2752</v>
+        <v>36.5</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>2359.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>2461.1</v>
+        <v>92.8</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>1856.2</v>
-      </c>
-      <c r="L6" s="18" t="n">
-        <v>14965.1</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -15302,22 +15368,19 @@
         </is>
       </c>
       <c r="G7" s="19" t="n">
-        <v>5644.6</v>
+        <v>23.6</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>2813.1</v>
+        <v>36.5</v>
       </c>
       <c r="I7" s="19" t="n">
-        <v>2416.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J7" s="19" t="n">
-        <v>2518</v>
+        <v>92.8</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>1893.4</v>
-      </c>
-      <c r="L7" s="19" t="n">
-        <v>15285.4</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -15340,22 +15403,19 @@
         </is>
       </c>
       <c r="G8" s="19" t="n">
-        <v>5700.1</v>
+        <v>23.6</v>
       </c>
       <c r="H8" s="19" t="n">
-        <v>2844.3</v>
+        <v>36.5</v>
       </c>
       <c r="I8" s="19" t="n">
-        <v>2445.4</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J8" s="19" t="n">
-        <v>2547</v>
+        <v>92.8</v>
       </c>
       <c r="K8" s="19" t="n">
-        <v>1912.5</v>
-      </c>
-      <c r="L8" s="19" t="n">
-        <v>15449.3</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -15378,22 +15438,19 @@
         </is>
       </c>
       <c r="G9" s="19" t="n">
-        <v>5756.6</v>
+        <v>23.6</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>2876</v>
+        <v>36.5</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>2474.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>2576.5</v>
+        <v>92.8</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>1931.8</v>
-      </c>
-      <c r="L9" s="19" t="n">
-        <v>15615.7</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -15416,22 +15473,19 @@
         </is>
       </c>
       <c r="G10" s="19" t="n">
-        <v>5796.9</v>
+        <v>23.6</v>
       </c>
       <c r="H10" s="19" t="n">
-        <v>2898.7</v>
+        <v>36.5</v>
       </c>
       <c r="I10" s="19" t="n">
-        <v>2495.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J10" s="19" t="n">
-        <v>2597.6</v>
+        <v>92.8</v>
       </c>
       <c r="K10" s="19" t="n">
-        <v>1945.6</v>
-      </c>
-      <c r="L10" s="19" t="n">
-        <v>15734.3</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -15454,22 +15508,19 @@
         </is>
       </c>
       <c r="G11" s="19" t="n">
-        <v>6225.1</v>
+        <v>23.6</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>3135.1</v>
+        <v>36.5</v>
       </c>
       <c r="I11" s="19" t="n">
-        <v>2730</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J11" s="19" t="n">
-        <v>2818.3</v>
+        <v>92.8</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>2095.2</v>
-      </c>
-      <c r="L11" s="19" t="n">
-        <v>17003.7</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -15492,22 +15543,19 @@
         </is>
       </c>
       <c r="G12" s="19" t="n">
-        <v>6411</v>
+        <v>23.6</v>
       </c>
       <c r="H12" s="19" t="n">
-        <v>3229.3</v>
+        <v>36.5</v>
       </c>
       <c r="I12" s="19" t="n">
-        <v>2819.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J12" s="19" t="n">
-        <v>2903.9</v>
+        <v>92.8</v>
       </c>
       <c r="K12" s="19" t="n">
-        <v>2159.1</v>
-      </c>
-      <c r="L12" s="19" t="n">
-        <v>17522.5</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -15530,22 +15578,19 @@
         </is>
       </c>
       <c r="G13" s="19" t="n">
-        <v>6144</v>
+        <v>23.6</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>3084.3</v>
+        <v>36.5</v>
       </c>
       <c r="I13" s="19" t="n">
-        <v>2679.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J13" s="19" t="n">
-        <v>2769.5</v>
+        <v>92.8</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>2066.6</v>
-      </c>
-      <c r="L13" s="19" t="n">
-        <v>16743.7</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -15568,22 +15613,19 @@
         </is>
       </c>
       <c r="G14" s="19" t="n">
-        <v>6095</v>
+        <v>23.6</v>
       </c>
       <c r="H14" s="19" t="n">
-        <v>3068</v>
+        <v>36.5</v>
       </c>
       <c r="I14" s="19" t="n">
-        <v>2660.9</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J14" s="19" t="n">
-        <v>2756.4</v>
+        <v>92.8</v>
       </c>
       <c r="K14" s="19" t="n">
-        <v>2049.4</v>
-      </c>
-      <c r="L14" s="19" t="n">
-        <v>16629.7</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -15606,29 +15648,30 @@
 （実績）</t>
         </is>
       </c>
-      <c r="E15" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>0</v>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="G15" s="18" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>7.3</v>
+        <v>4.1</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="L15" s="18" t="n">
-        <v>33</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -15640,29 +15683,30 @@
           <t>令和9年度</t>
         </is>
       </c>
-      <c r="E16" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="19" t="n">
-        <v>0</v>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F16" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="G16" s="19" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J16" s="19" t="n">
-        <v>7.5</v>
+        <v>4.1</v>
       </c>
       <c r="K16" s="19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="L16" s="19" t="n">
-        <v>33.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -15674,29 +15718,30 @@
           <t>令和10年度</t>
         </is>
       </c>
-      <c r="E17" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="19" t="n">
-        <v>0</v>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F17" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="G17" s="19" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="K17" s="19" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="L17" s="19" t="n">
-        <v>34</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -15708,29 +15753,30 @@
           <t>令和11年度</t>
         </is>
       </c>
-      <c r="E18" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="19" t="n">
-        <v>0</v>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="G18" s="19" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="H18" s="19" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J18" s="19" t="n">
-        <v>7.7</v>
+        <v>4.1</v>
       </c>
       <c r="K18" s="19" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="L18" s="19" t="n">
-        <v>34.4</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -15742,29 +15788,30 @@
           <t>令和12年度</t>
         </is>
       </c>
-      <c r="E19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="19" t="n">
-        <v>0</v>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F19" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="G19" s="19" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J19" s="19" t="n">
-        <v>7.7</v>
+        <v>4.1</v>
       </c>
       <c r="K19" s="19" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="L19" s="19" t="n">
-        <v>34.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -15776,29 +15823,30 @@
           <t>令和17年度</t>
         </is>
       </c>
-      <c r="E20" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="19" t="n">
-        <v>0</v>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="G20" s="19" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="H20" s="19" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="I20" s="19" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J20" s="19" t="n">
-        <v>8.4</v>
+        <v>4.1</v>
       </c>
       <c r="K20" s="19" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="L20" s="19" t="n">
-        <v>37.4</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -15810,29 +15858,30 @@
           <t>令和22年度</t>
         </is>
       </c>
-      <c r="E21" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="19" t="n">
-        <v>0</v>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F21" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="G21" s="19" t="n">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J21" s="19" t="n">
-        <v>8.6</v>
+        <v>4.1</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="L21" s="19" t="n">
-        <v>38.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -15844,29 +15893,30 @@
           <t>令和27年度</t>
         </is>
       </c>
-      <c r="E22" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="19" t="n">
-        <v>0</v>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F22" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="G22" s="19" t="n">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="I22" s="19" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J22" s="19" t="n">
-        <v>8.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="K22" s="19" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="L22" s="19" t="n">
-        <v>36.8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -15878,29 +15928,30 @@
           <t>令和32年度</t>
         </is>
       </c>
-      <c r="E23" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="19" t="n">
-        <v>0</v>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F23" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="G23" s="19" t="n">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J23" s="19" t="n">
-        <v>8.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="K23" s="19" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="L23" s="19" t="n">
-        <v>36.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -15924,28 +15975,25 @@
         </is>
       </c>
       <c r="E24" s="18" t="n">
-        <v>43.5</v>
+        <v>3.9</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>60.1</v>
+        <v>4.5</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>360.7</v>
+        <v>6</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>223.2</v>
+        <v>7</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>121.4</v>
+        <v>8</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>133.2</v>
+        <v>13</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>133.9</v>
-      </c>
-      <c r="L24" s="18" t="n">
-        <v>1076</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -15958,28 +16006,25 @@
         </is>
       </c>
       <c r="E25" s="19" t="n">
-        <v>44.3</v>
+        <v>3.9</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>61.3</v>
+        <v>4.5</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>367.8</v>
+        <v>6</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>228.1</v>
+        <v>7</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>124.4</v>
+        <v>8</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>136.2</v>
+        <v>13</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>136.6</v>
-      </c>
-      <c r="L25" s="19" t="n">
-        <v>1098.7</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -15992,28 +16037,25 @@
         </is>
       </c>
       <c r="E26" s="19" t="n">
-        <v>44.7</v>
+        <v>3.9</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>61.9</v>
+        <v>4.5</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>371.4</v>
+        <v>6</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>230.6</v>
+        <v>7</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>125.9</v>
+        <v>8</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>137.8</v>
+        <v>13</v>
       </c>
       <c r="K26" s="19" t="n">
-        <v>138</v>
-      </c>
-      <c r="L26" s="19" t="n">
-        <v>1110.3</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -16026,28 +16068,25 @@
         </is>
       </c>
       <c r="E27" s="19" t="n">
-        <v>45.2</v>
+        <v>3.9</v>
       </c>
       <c r="F27" s="19" t="n">
-        <v>62.4</v>
+        <v>4.5</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>375.1</v>
+        <v>6</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>233.2</v>
+        <v>7</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>127.4</v>
+        <v>8</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>139.4</v>
+        <v>13</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>139.4</v>
-      </c>
-      <c r="L27" s="19" t="n">
-        <v>1122.1</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -16060,28 +16099,25 @@
         </is>
       </c>
       <c r="E28" s="19" t="n">
-        <v>45.5</v>
+        <v>3.9</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>62.9</v>
+        <v>4.5</v>
       </c>
       <c r="G28" s="19" t="n">
-        <v>377.7</v>
+        <v>6</v>
       </c>
       <c r="H28" s="19" t="n">
-        <v>235.1</v>
+        <v>7</v>
       </c>
       <c r="I28" s="19" t="n">
-        <v>128.5</v>
+        <v>8</v>
       </c>
       <c r="J28" s="19" t="n">
-        <v>140.5</v>
+        <v>13</v>
       </c>
       <c r="K28" s="19" t="n">
-        <v>140.3</v>
-      </c>
-      <c r="L28" s="19" t="n">
-        <v>1130.5</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -16094,28 +16130,25 @@
         </is>
       </c>
       <c r="E29" s="19" t="n">
-        <v>47.4</v>
+        <v>3.9</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>65.7</v>
+        <v>4.5</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>405.6</v>
+        <v>6</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>254.2</v>
+        <v>7</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>140.5</v>
+        <v>8</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>152.5</v>
+        <v>13</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>151.2</v>
-      </c>
-      <c r="L29" s="19" t="n">
-        <v>1217.1</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -16128,28 +16161,25 @@
         </is>
       </c>
       <c r="E30" s="19" t="n">
-        <v>48.3</v>
+        <v>3.9</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>66.90000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>417.7</v>
+        <v>6</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>261.9</v>
+        <v>7</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>145.1</v>
+        <v>8</v>
       </c>
       <c r="J30" s="19" t="n">
-        <v>157.1</v>
+        <v>13</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>155.8</v>
-      </c>
-      <c r="L30" s="19" t="n">
-        <v>1252.8</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -16162,28 +16192,25 @@
         </is>
       </c>
       <c r="E31" s="19" t="n">
-        <v>46.8</v>
+        <v>3.9</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>64.90000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>400.3</v>
+        <v>6</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>250.1</v>
+        <v>7</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>137.9</v>
+        <v>8</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>149.9</v>
+        <v>13</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>149.1</v>
-      </c>
-      <c r="L31" s="19" t="n">
-        <v>1199</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -16196,28 +16223,25 @@
         </is>
       </c>
       <c r="E32" s="19" t="n">
-        <v>47.2</v>
+        <v>3.9</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>65.3</v>
+        <v>4.5</v>
       </c>
       <c r="G32" s="19" t="n">
-        <v>397.1</v>
+        <v>6</v>
       </c>
       <c r="H32" s="19" t="n">
-        <v>248.8</v>
+        <v>7</v>
       </c>
       <c r="I32" s="19" t="n">
-        <v>137</v>
+        <v>8</v>
       </c>
       <c r="J32" s="19" t="n">
-        <v>149.2</v>
+        <v>13</v>
       </c>
       <c r="K32" s="19" t="n">
-        <v>147.8</v>
-      </c>
-      <c r="L32" s="19" t="n">
-        <v>1192.4</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -16241,28 +16265,25 @@
         </is>
       </c>
       <c r="E33" s="18" t="n">
-        <v>32.9</v>
+        <v>7.6</v>
       </c>
       <c r="F33" s="18" t="n">
-        <v>107.4</v>
+        <v>11.3</v>
       </c>
       <c r="G33" s="18" t="n">
-        <v>236.7</v>
+        <v>10.3</v>
       </c>
       <c r="H33" s="18" t="n">
-        <v>196.7</v>
+        <v>12.4</v>
       </c>
       <c r="I33" s="18" t="n">
-        <v>91.59999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="J33" s="18" t="n">
-        <v>44.8</v>
+        <v>10.3</v>
       </c>
       <c r="K33" s="18" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="L33" s="18" t="n">
-        <v>764.6</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -16275,28 +16296,25 @@
         </is>
       </c>
       <c r="E34" s="19" t="n">
-        <v>33.5</v>
+        <v>7.6</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>109.5</v>
+        <v>11.3</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>241.3</v>
+        <v>10.3</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>201.1</v>
+        <v>12.4</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>93.8</v>
+        <v>14.2</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>45.9</v>
+        <v>10.3</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="L34" s="19" t="n">
-        <v>780.7</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -16309,28 +16327,25 @@
         </is>
       </c>
       <c r="E35" s="19" t="n">
-        <v>33.9</v>
+        <v>7.6</v>
       </c>
       <c r="F35" s="19" t="n">
-        <v>110.5</v>
+        <v>11.3</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>243.7</v>
+        <v>10.3</v>
       </c>
       <c r="H35" s="19" t="n">
-        <v>203.3</v>
+        <v>12.4</v>
       </c>
       <c r="I35" s="19" t="n">
-        <v>94.90000000000001</v>
+        <v>14.2</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>46.4</v>
+        <v>10.3</v>
       </c>
       <c r="K35" s="19" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="L35" s="19" t="n">
-        <v>788.9</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -16343,28 +16358,25 @@
         </is>
       </c>
       <c r="E36" s="19" t="n">
-        <v>34.2</v>
+        <v>7.6</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>111.6</v>
+        <v>11.3</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>246.1</v>
+        <v>10.3</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>205.6</v>
+        <v>12.4</v>
       </c>
       <c r="I36" s="19" t="n">
-        <v>96</v>
+        <v>14.2</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>46.9</v>
+        <v>10.3</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="L36" s="19" t="n">
-        <v>797.2</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -16377,28 +16389,25 @@
         </is>
       </c>
       <c r="E37" s="19" t="n">
-        <v>34.4</v>
+        <v>7.6</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>112.5</v>
+        <v>11.3</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>247.8</v>
+        <v>10.3</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>207.3</v>
+        <v>12.4</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>96.8</v>
+        <v>14.2</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>47.3</v>
+        <v>10.3</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="L37" s="19" t="n">
-        <v>803.3</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -16411,28 +16420,25 @@
         </is>
       </c>
       <c r="E38" s="19" t="n">
-        <v>35.9</v>
+        <v>7.6</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>117.4</v>
+        <v>11.3</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>266.1</v>
+        <v>10.3</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>224.2</v>
+        <v>12.4</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>105.9</v>
+        <v>14.2</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>51.3</v>
+        <v>10.3</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="L38" s="19" t="n">
-        <v>862.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -16445,28 +16451,25 @@
         </is>
       </c>
       <c r="E39" s="19" t="n">
-        <v>36.5</v>
+        <v>7.6</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>119.6</v>
+        <v>11.3</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>274.1</v>
+        <v>10.3</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>230.9</v>
+        <v>12.4</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>109.4</v>
+        <v>14.2</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>52.9</v>
+        <v>10.3</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="L39" s="19" t="n">
-        <v>886.8</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -16479,28 +16482,25 @@
         </is>
       </c>
       <c r="E40" s="19" t="n">
-        <v>35.5</v>
+        <v>7.6</v>
       </c>
       <c r="F40" s="19" t="n">
-        <v>115.9</v>
+        <v>11.3</v>
       </c>
       <c r="G40" s="19" t="n">
-        <v>262.7</v>
+        <v>10.3</v>
       </c>
       <c r="H40" s="19" t="n">
-        <v>220.5</v>
+        <v>12.4</v>
       </c>
       <c r="I40" s="19" t="n">
-        <v>104</v>
+        <v>14.2</v>
       </c>
       <c r="J40" s="19" t="n">
-        <v>50.4</v>
+        <v>10.3</v>
       </c>
       <c r="K40" s="19" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="L40" s="19" t="n">
-        <v>849.7</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -16513,28 +16513,25 @@
         </is>
       </c>
       <c r="E41" s="19" t="n">
-        <v>35.7</v>
+        <v>7.6</v>
       </c>
       <c r="F41" s="19" t="n">
-        <v>116.8</v>
+        <v>11.3</v>
       </c>
       <c r="G41" s="19" t="n">
-        <v>260.6</v>
+        <v>10.3</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>219.3</v>
+        <v>12.4</v>
       </c>
       <c r="I41" s="19" t="n">
-        <v>103.3</v>
+        <v>14.2</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>50.2</v>
+        <v>10.3</v>
       </c>
       <c r="K41" s="19" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="L41" s="19" t="n">
-        <v>846.1</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -16568,22 +16565,19 @@
         </is>
       </c>
       <c r="G42" s="18" t="n">
-        <v>434</v>
+        <v>8.4</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>193</v>
+        <v>7.5</v>
       </c>
       <c r="I42" s="18" t="n">
-        <v>93.90000000000001</v>
+        <v>10</v>
       </c>
       <c r="J42" s="18" t="n">
-        <v>102</v>
+        <v>11.2</v>
       </c>
       <c r="K42" s="18" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="L42" s="18" t="n">
-        <v>850.6</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -16606,22 +16600,19 @@
         </is>
       </c>
       <c r="G43" s="19" t="n">
-        <v>442.5</v>
+        <v>8.4</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>197.3</v>
+        <v>7.5</v>
       </c>
       <c r="I43" s="19" t="n">
-        <v>96.2</v>
+        <v>10</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>104.3</v>
+        <v>11.2</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="L43" s="19" t="n">
-        <v>868.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -16644,22 +16635,19 @@
         </is>
       </c>
       <c r="G44" s="19" t="n">
-        <v>446.9</v>
+        <v>8.4</v>
       </c>
       <c r="H44" s="19" t="n">
-        <v>199.4</v>
+        <v>7.5</v>
       </c>
       <c r="I44" s="19" t="n">
-        <v>97.40000000000001</v>
+        <v>10</v>
       </c>
       <c r="J44" s="19" t="n">
-        <v>105.5</v>
+        <v>11.2</v>
       </c>
       <c r="K44" s="19" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="L44" s="19" t="n">
-        <v>877.7</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -16682,22 +16670,19 @@
         </is>
       </c>
       <c r="G45" s="19" t="n">
-        <v>451.3</v>
+        <v>8.4</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>201.7</v>
+        <v>7.5</v>
       </c>
       <c r="I45" s="19" t="n">
-        <v>98.5</v>
+        <v>10</v>
       </c>
       <c r="J45" s="19" t="n">
-        <v>106.7</v>
+        <v>11.2</v>
       </c>
       <c r="K45" s="19" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="L45" s="19" t="n">
-        <v>887</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -16720,22 +16705,19 @@
         </is>
       </c>
       <c r="G46" s="19" t="n">
-        <v>454.4</v>
+        <v>8.4</v>
       </c>
       <c r="H46" s="19" t="n">
-        <v>203.3</v>
+        <v>7.5</v>
       </c>
       <c r="I46" s="19" t="n">
-        <v>99.40000000000001</v>
+        <v>10</v>
       </c>
       <c r="J46" s="19" t="n">
-        <v>107.6</v>
+        <v>11.2</v>
       </c>
       <c r="K46" s="19" t="n">
-        <v>29</v>
-      </c>
-      <c r="L46" s="19" t="n">
-        <v>893.7</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -16758,22 +16740,19 @@
         </is>
       </c>
       <c r="G47" s="19" t="n">
-        <v>488</v>
+        <v>8.4</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>219.9</v>
+        <v>7.5</v>
       </c>
       <c r="I47" s="19" t="n">
-        <v>108.7</v>
+        <v>10</v>
       </c>
       <c r="J47" s="19" t="n">
-        <v>116.8</v>
+        <v>11.2</v>
       </c>
       <c r="K47" s="19" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="L47" s="19" t="n">
-        <v>964.6</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -16796,22 +16775,19 @@
         </is>
       </c>
       <c r="G48" s="19" t="n">
-        <v>502.6</v>
+        <v>8.4</v>
       </c>
       <c r="H48" s="19" t="n">
-        <v>226.5</v>
+        <v>7.5</v>
       </c>
       <c r="I48" s="19" t="n">
-        <v>112.2</v>
+        <v>10</v>
       </c>
       <c r="J48" s="19" t="n">
-        <v>120.3</v>
+        <v>11.2</v>
       </c>
       <c r="K48" s="19" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="L48" s="19" t="n">
-        <v>993.8</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -16834,22 +16810,19 @@
         </is>
       </c>
       <c r="G49" s="19" t="n">
-        <v>481.7</v>
+        <v>8.4</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>216.3</v>
+        <v>7.5</v>
       </c>
       <c r="I49" s="19" t="n">
-        <v>106.7</v>
+        <v>10</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>114.7</v>
+        <v>11.2</v>
       </c>
       <c r="K49" s="19" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="L49" s="19" t="n">
-        <v>950.2</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -16872,22 +16845,19 @@
         </is>
       </c>
       <c r="G50" s="19" t="n">
-        <v>477.8</v>
+        <v>8.4</v>
       </c>
       <c r="H50" s="19" t="n">
-        <v>215.2</v>
+        <v>7.5</v>
       </c>
       <c r="I50" s="19" t="n">
-        <v>105.9</v>
+        <v>10</v>
       </c>
       <c r="J50" s="19" t="n">
-        <v>114.2</v>
+        <v>11.2</v>
       </c>
       <c r="K50" s="19" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="L50" s="19" t="n">
-        <v>943.7</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -16921,22 +16891,19 @@
         </is>
       </c>
       <c r="G51" s="18" t="n">
-        <v>292.4</v>
+        <v>6.8</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>186</v>
+        <v>8.5</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>68.40000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>30.2</v>
+        <v>10.7</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="L51" s="18" t="n">
-        <v>600.7</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -16959,22 +16926,19 @@
         </is>
       </c>
       <c r="G52" s="19" t="n">
-        <v>298.2</v>
+        <v>6.8</v>
       </c>
       <c r="H52" s="19" t="n">
-        <v>190.1</v>
+        <v>8.5</v>
       </c>
       <c r="I52" s="19" t="n">
-        <v>70</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J52" s="19" t="n">
-        <v>30.9</v>
+        <v>10.7</v>
       </c>
       <c r="K52" s="19" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="L52" s="19" t="n">
-        <v>613.3</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -16997,22 +16961,19 @@
         </is>
       </c>
       <c r="G53" s="19" t="n">
-        <v>301.1</v>
+        <v>6.8</v>
       </c>
       <c r="H53" s="19" t="n">
-        <v>192.2</v>
+        <v>8.5</v>
       </c>
       <c r="I53" s="19" t="n">
-        <v>70.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J53" s="19" t="n">
-        <v>31.3</v>
+        <v>10.7</v>
       </c>
       <c r="K53" s="19" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="L53" s="19" t="n">
-        <v>619.8</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -17035,22 +16996,19 @@
         </is>
       </c>
       <c r="G54" s="19" t="n">
-        <v>304.1</v>
+        <v>6.8</v>
       </c>
       <c r="H54" s="19" t="n">
-        <v>194.4</v>
+        <v>8.5</v>
       </c>
       <c r="I54" s="19" t="n">
-        <v>71.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J54" s="19" t="n">
-        <v>31.6</v>
+        <v>10.7</v>
       </c>
       <c r="K54" s="19" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="L54" s="19" t="n">
-        <v>626.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -17073,22 +17031,19 @@
         </is>
       </c>
       <c r="G55" s="19" t="n">
-        <v>306.2</v>
+        <v>6.8</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>195.9</v>
+        <v>8.5</v>
       </c>
       <c r="I55" s="19" t="n">
-        <v>72.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J55" s="19" t="n">
-        <v>31.9</v>
+        <v>10.7</v>
       </c>
       <c r="K55" s="19" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="L55" s="19" t="n">
-        <v>631.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -17111,22 +17066,19 @@
         </is>
       </c>
       <c r="G56" s="19" t="n">
-        <v>328.8</v>
+        <v>6.8</v>
       </c>
       <c r="H56" s="19" t="n">
-        <v>211.9</v>
+        <v>8.5</v>
       </c>
       <c r="I56" s="19" t="n">
-        <v>79.09999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J56" s="19" t="n">
-        <v>34.6</v>
+        <v>10.7</v>
       </c>
       <c r="K56" s="19" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="L56" s="19" t="n">
-        <v>681.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -17149,22 +17101,19 @@
         </is>
       </c>
       <c r="G57" s="19" t="n">
-        <v>338.6</v>
+        <v>6.8</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>218.2</v>
+        <v>8.5</v>
       </c>
       <c r="I57" s="19" t="n">
-        <v>81.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J57" s="19" t="n">
-        <v>35.7</v>
+        <v>10.7</v>
       </c>
       <c r="K57" s="19" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="L57" s="19" t="n">
-        <v>701.7</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -17187,22 +17136,19 @@
         </is>
       </c>
       <c r="G58" s="19" t="n">
-        <v>324.6</v>
+        <v>6.8</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>208.4</v>
+        <v>8.5</v>
       </c>
       <c r="I58" s="19" t="n">
-        <v>77.59999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J58" s="19" t="n">
-        <v>34</v>
+        <v>10.7</v>
       </c>
       <c r="K58" s="19" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="L58" s="19" t="n">
-        <v>671</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -17225,22 +17171,19 @@
         </is>
       </c>
       <c r="G59" s="19" t="n">
-        <v>322</v>
+        <v>6.8</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>207.3</v>
+        <v>8.5</v>
       </c>
       <c r="I59" s="19" t="n">
-        <v>77.09999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J59" s="19" t="n">
-        <v>33.9</v>
+        <v>10.7</v>
       </c>
       <c r="K59" s="19" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="L59" s="19" t="n">
-        <v>666.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -17270,22 +17213,19 @@
         <v>0</v>
       </c>
       <c r="G60" s="18" t="n">
-        <v>697.2</v>
+        <v>6.6</v>
       </c>
       <c r="H60" s="18" t="n">
-        <v>370.3</v>
+        <v>7.7</v>
       </c>
       <c r="I60" s="18" t="n">
-        <v>142.7</v>
+        <v>8</v>
       </c>
       <c r="J60" s="18" t="n">
-        <v>96.3</v>
+        <v>7.6</v>
       </c>
       <c r="K60" s="18" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="L60" s="18" t="n">
-        <v>1354</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -17304,22 +17244,19 @@
         <v>0</v>
       </c>
       <c r="G61" s="19" t="n">
-        <v>710.9</v>
+        <v>6.6</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>378.5</v>
+        <v>7.7</v>
       </c>
       <c r="I61" s="19" t="n">
-        <v>146.1</v>
+        <v>8</v>
       </c>
       <c r="J61" s="19" t="n">
-        <v>98.5</v>
+        <v>7.6</v>
       </c>
       <c r="K61" s="19" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="L61" s="19" t="n">
-        <v>1382.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -17338,22 +17275,19 @@
         <v>0</v>
       </c>
       <c r="G62" s="19" t="n">
-        <v>717.9</v>
+        <v>6.6</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>382.7</v>
+        <v>7.7</v>
       </c>
       <c r="I62" s="19" t="n">
-        <v>147.8</v>
+        <v>8</v>
       </c>
       <c r="J62" s="19" t="n">
-        <v>99.7</v>
+        <v>7.6</v>
       </c>
       <c r="K62" s="19" t="n">
-        <v>49</v>
-      </c>
-      <c r="L62" s="19" t="n">
-        <v>1397.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -17372,22 +17306,19 @@
         <v>0</v>
       </c>
       <c r="G63" s="19" t="n">
-        <v>725</v>
+        <v>6.6</v>
       </c>
       <c r="H63" s="19" t="n">
-        <v>387</v>
+        <v>7.7</v>
       </c>
       <c r="I63" s="19" t="n">
-        <v>149.6</v>
+        <v>8</v>
       </c>
       <c r="J63" s="19" t="n">
-        <v>100.8</v>
+        <v>7.6</v>
       </c>
       <c r="K63" s="19" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="L63" s="19" t="n">
-        <v>1411.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -17406,22 +17337,19 @@
         <v>0</v>
       </c>
       <c r="G64" s="19" t="n">
-        <v>730</v>
+        <v>6.6</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>390.1</v>
+        <v>7.7</v>
       </c>
       <c r="I64" s="19" t="n">
-        <v>150.9</v>
+        <v>8</v>
       </c>
       <c r="J64" s="19" t="n">
-        <v>101.6</v>
+        <v>7.6</v>
       </c>
       <c r="K64" s="19" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="L64" s="19" t="n">
-        <v>1422.4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -17440,22 +17368,19 @@
         <v>0</v>
       </c>
       <c r="G65" s="19" t="n">
-        <v>783.9</v>
+        <v>6.6</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>421.9</v>
+        <v>7.7</v>
       </c>
       <c r="I65" s="19" t="n">
-        <v>165</v>
+        <v>8</v>
       </c>
       <c r="J65" s="19" t="n">
-        <v>110.3</v>
+        <v>7.6</v>
       </c>
       <c r="K65" s="19" t="n">
-        <v>53.7</v>
-      </c>
-      <c r="L65" s="19" t="n">
-        <v>1534.8</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -17474,22 +17399,19 @@
         <v>0</v>
       </c>
       <c r="G66" s="19" t="n">
-        <v>807.4</v>
+        <v>6.6</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>434.5</v>
+        <v>7.7</v>
       </c>
       <c r="I66" s="19" t="n">
-        <v>170.5</v>
+        <v>8</v>
       </c>
       <c r="J66" s="19" t="n">
-        <v>113.6</v>
+        <v>7.6</v>
       </c>
       <c r="K66" s="19" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="L66" s="19" t="n">
-        <v>1581.3</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -17508,22 +17430,19 @@
         <v>0</v>
       </c>
       <c r="G67" s="19" t="n">
-        <v>773.7</v>
+        <v>6.6</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>415</v>
+        <v>7.7</v>
       </c>
       <c r="I67" s="19" t="n">
-        <v>162</v>
+        <v>8</v>
       </c>
       <c r="J67" s="19" t="n">
-        <v>108.4</v>
+        <v>7.6</v>
       </c>
       <c r="K67" s="19" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="L67" s="19" t="n">
-        <v>1512</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -17542,22 +17461,19 @@
         <v>0</v>
       </c>
       <c r="G68" s="19" t="n">
-        <v>767.6</v>
+        <v>6.6</v>
       </c>
       <c r="H68" s="19" t="n">
-        <v>412.8</v>
+        <v>7.7</v>
       </c>
       <c r="I68" s="19" t="n">
-        <v>160.9</v>
+        <v>8</v>
       </c>
       <c r="J68" s="19" t="n">
-        <v>107.8</v>
+        <v>7.6</v>
       </c>
       <c r="K68" s="19" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="L68" s="19" t="n">
-        <v>1501.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -17581,28 +17497,25 @@
         </is>
       </c>
       <c r="E69" s="18" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="F69" s="18" t="n">
-        <v>7.2</v>
+        <v>10.6</v>
       </c>
       <c r="G69" s="18" t="n">
-        <v>75.59999999999999</v>
+        <v>11.9</v>
       </c>
       <c r="H69" s="18" t="n">
-        <v>122.6</v>
+        <v>10.8</v>
       </c>
       <c r="I69" s="18" t="n">
-        <v>40.2</v>
+        <v>16.7</v>
       </c>
       <c r="J69" s="18" t="n">
-        <v>41.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K69" s="18" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="L69" s="18" t="n">
-        <v>306.1</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -17615,28 +17528,25 @@
         </is>
       </c>
       <c r="E70" s="19" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="F70" s="19" t="n">
-        <v>7.4</v>
+        <v>10.6</v>
       </c>
       <c r="G70" s="19" t="n">
-        <v>77</v>
+        <v>11.9</v>
       </c>
       <c r="H70" s="19" t="n">
-        <v>125.4</v>
+        <v>10.8</v>
       </c>
       <c r="I70" s="19" t="n">
-        <v>41.2</v>
+        <v>16.7</v>
       </c>
       <c r="J70" s="19" t="n">
-        <v>42.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K70" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="L70" s="19" t="n">
-        <v>312.8</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -17649,28 +17559,25 @@
         </is>
       </c>
       <c r="E71" s="19" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="F71" s="19" t="n">
-        <v>7.5</v>
+        <v>10.6</v>
       </c>
       <c r="G71" s="19" t="n">
-        <v>77.8</v>
+        <v>11.9</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>126.7</v>
+        <v>10.8</v>
       </c>
       <c r="I71" s="19" t="n">
-        <v>41.7</v>
+        <v>16.7</v>
       </c>
       <c r="J71" s="19" t="n">
-        <v>42.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K71" s="19" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="L71" s="19" t="n">
-        <v>316.2</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -17683,28 +17590,25 @@
         </is>
       </c>
       <c r="E72" s="19" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="F72" s="19" t="n">
-        <v>7.5</v>
+        <v>10.6</v>
       </c>
       <c r="G72" s="19" t="n">
-        <v>78.59999999999999</v>
+        <v>11.9</v>
       </c>
       <c r="H72" s="19" t="n">
-        <v>128.2</v>
+        <v>10.8</v>
       </c>
       <c r="I72" s="19" t="n">
-        <v>42.2</v>
+        <v>16.7</v>
       </c>
       <c r="J72" s="19" t="n">
-        <v>43.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K72" s="19" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="L72" s="19" t="n">
-        <v>319.7</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -17717,28 +17621,25 @@
         </is>
       </c>
       <c r="E73" s="19" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="F73" s="19" t="n">
-        <v>7.6</v>
+        <v>10.6</v>
       </c>
       <c r="G73" s="19" t="n">
-        <v>79.09999999999999</v>
+        <v>11.9</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>129.2</v>
+        <v>10.8</v>
       </c>
       <c r="I73" s="19" t="n">
-        <v>42.5</v>
+        <v>16.7</v>
       </c>
       <c r="J73" s="19" t="n">
-        <v>43.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K73" s="19" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="L73" s="19" t="n">
-        <v>322.1</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -17751,28 +17652,25 @@
         </is>
       </c>
       <c r="E74" s="19" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="F74" s="19" t="n">
-        <v>7.9</v>
+        <v>10.6</v>
       </c>
       <c r="G74" s="19" t="n">
-        <v>85</v>
+        <v>11.9</v>
       </c>
       <c r="H74" s="19" t="n">
-        <v>139.7</v>
+        <v>10.8</v>
       </c>
       <c r="I74" s="19" t="n">
-        <v>46.5</v>
+        <v>16.7</v>
       </c>
       <c r="J74" s="19" t="n">
-        <v>47.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K74" s="19" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="L74" s="19" t="n">
-        <v>347.9</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -17785,28 +17683,25 @@
         </is>
       </c>
       <c r="E75" s="19" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="F75" s="19" t="n">
-        <v>8.1</v>
+        <v>10.6</v>
       </c>
       <c r="G75" s="19" t="n">
-        <v>87.5</v>
+        <v>11.9</v>
       </c>
       <c r="H75" s="19" t="n">
-        <v>143.9</v>
+        <v>10.8</v>
       </c>
       <c r="I75" s="19" t="n">
-        <v>48.1</v>
+        <v>16.7</v>
       </c>
       <c r="J75" s="19" t="n">
-        <v>48.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K75" s="19" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="L75" s="19" t="n">
-        <v>358.4</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -17819,28 +17714,25 @@
         </is>
       </c>
       <c r="E76" s="19" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="F76" s="19" t="n">
-        <v>7.8</v>
+        <v>10.6</v>
       </c>
       <c r="G76" s="19" t="n">
-        <v>83.8</v>
+        <v>11.9</v>
       </c>
       <c r="H76" s="19" t="n">
-        <v>137.4</v>
+        <v>10.8</v>
       </c>
       <c r="I76" s="19" t="n">
-        <v>45.7</v>
+        <v>16.7</v>
       </c>
       <c r="J76" s="19" t="n">
-        <v>46.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K76" s="19" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="L76" s="19" t="n">
-        <v>342.5</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -17853,28 +17745,25 @@
         </is>
       </c>
       <c r="E77" s="19" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="F77" s="19" t="n">
-        <v>7.9</v>
+        <v>10.6</v>
       </c>
       <c r="G77" s="19" t="n">
-        <v>83.2</v>
+        <v>11.9</v>
       </c>
       <c r="H77" s="19" t="n">
-        <v>136.7</v>
+        <v>10.8</v>
       </c>
       <c r="I77" s="19" t="n">
-        <v>45.4</v>
+        <v>16.7</v>
       </c>
       <c r="J77" s="19" t="n">
-        <v>46.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K77" s="19" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="L77" s="19" t="n">
-        <v>340.6</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -17898,28 +17787,25 @@
         </is>
       </c>
       <c r="E78" s="18" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>17.4</v>
+        <v>4</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>31.7</v>
+        <v>5.1</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>16.9</v>
+        <v>7.2</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>25.6</v>
+        <v>8.5</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="L78" s="18" t="n">
-        <v>100.6</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -17932,28 +17818,25 @@
         </is>
       </c>
       <c r="E79" s="19" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="F79" s="19" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="G79" s="19" t="n">
-        <v>17.7</v>
+        <v>4</v>
       </c>
       <c r="H79" s="19" t="n">
-        <v>32.4</v>
+        <v>5.1</v>
       </c>
       <c r="I79" s="19" t="n">
-        <v>17.3</v>
+        <v>7.2</v>
       </c>
       <c r="J79" s="19" t="n">
-        <v>26.2</v>
+        <v>8.5</v>
       </c>
       <c r="K79" s="19" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="L79" s="19" t="n">
-        <v>102.7</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -17966,28 +17849,25 @@
         </is>
       </c>
       <c r="E80" s="19" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="F80" s="19" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="G80" s="19" t="n">
-        <v>17.9</v>
+        <v>4</v>
       </c>
       <c r="H80" s="19" t="n">
-        <v>32.8</v>
+        <v>5.1</v>
       </c>
       <c r="I80" s="19" t="n">
-        <v>17.5</v>
+        <v>7.2</v>
       </c>
       <c r="J80" s="19" t="n">
-        <v>26.5</v>
+        <v>8.5</v>
       </c>
       <c r="K80" s="19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L80" s="19" t="n">
-        <v>103.9</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -18000,28 +17880,25 @@
         </is>
       </c>
       <c r="E81" s="19" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="F81" s="19" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="G81" s="19" t="n">
-        <v>18.1</v>
+        <v>4</v>
       </c>
       <c r="H81" s="19" t="n">
-        <v>33.1</v>
+        <v>5.1</v>
       </c>
       <c r="I81" s="19" t="n">
-        <v>17.7</v>
+        <v>7.2</v>
       </c>
       <c r="J81" s="19" t="n">
-        <v>26.8</v>
+        <v>8.5</v>
       </c>
       <c r="K81" s="19" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="L81" s="19" t="n">
-        <v>105</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -18034,28 +17911,25 @@
         </is>
       </c>
       <c r="E82" s="19" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="F82" s="19" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="G82" s="19" t="n">
-        <v>18.2</v>
+        <v>4</v>
       </c>
       <c r="H82" s="19" t="n">
-        <v>33.4</v>
+        <v>5.1</v>
       </c>
       <c r="I82" s="19" t="n">
-        <v>17.9</v>
+        <v>7.2</v>
       </c>
       <c r="J82" s="19" t="n">
-        <v>27</v>
+        <v>8.5</v>
       </c>
       <c r="K82" s="19" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="L82" s="19" t="n">
-        <v>105.8</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -18068,28 +17942,25 @@
         </is>
       </c>
       <c r="E83" s="19" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="F83" s="19" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="G83" s="19" t="n">
-        <v>19.6</v>
+        <v>4</v>
       </c>
       <c r="H83" s="19" t="n">
-        <v>36.1</v>
+        <v>5.1</v>
       </c>
       <c r="I83" s="19" t="n">
-        <v>19.5</v>
+        <v>7.2</v>
       </c>
       <c r="J83" s="19" t="n">
-        <v>29.3</v>
+        <v>8.5</v>
       </c>
       <c r="K83" s="19" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="L83" s="19" t="n">
-        <v>114.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -18102,28 +17973,25 @@
         </is>
       </c>
       <c r="E84" s="19" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="F84" s="19" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="G84" s="19" t="n">
-        <v>20.2</v>
+        <v>4</v>
       </c>
       <c r="H84" s="19" t="n">
-        <v>37.2</v>
+        <v>5.1</v>
       </c>
       <c r="I84" s="19" t="n">
-        <v>20.2</v>
+        <v>7.2</v>
       </c>
       <c r="J84" s="19" t="n">
-        <v>30.2</v>
+        <v>8.5</v>
       </c>
       <c r="K84" s="19" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="L84" s="19" t="n">
-        <v>118</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -18136,28 +18004,25 @@
         </is>
       </c>
       <c r="E85" s="19" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="F85" s="19" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="G85" s="19" t="n">
-        <v>19.3</v>
+        <v>4</v>
       </c>
       <c r="H85" s="19" t="n">
-        <v>35.5</v>
+        <v>5.1</v>
       </c>
       <c r="I85" s="19" t="n">
-        <v>19.2</v>
+        <v>7.2</v>
       </c>
       <c r="J85" s="19" t="n">
-        <v>28.8</v>
+        <v>8.5</v>
       </c>
       <c r="K85" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="L85" s="19" t="n">
-        <v>112.7</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -18170,28 +18035,25 @@
         </is>
       </c>
       <c r="E86" s="19" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="F86" s="19" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="G86" s="19" t="n">
-        <v>19.1</v>
+        <v>4</v>
       </c>
       <c r="H86" s="19" t="n">
-        <v>35.4</v>
+        <v>5.1</v>
       </c>
       <c r="I86" s="19" t="n">
-        <v>19</v>
+        <v>7.2</v>
       </c>
       <c r="J86" s="19" t="n">
-        <v>28.7</v>
+        <v>8.5</v>
       </c>
       <c r="K86" s="19" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="L86" s="19" t="n">
-        <v>112</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -18214,29 +18076,40 @@
 （実績）</t>
         </is>
       </c>
-      <c r="E87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="18" t="n">
-        <v>0</v>
+      <c r="E87" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F87" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G87" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H87" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I87" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J87" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K87" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -18248,29 +18121,40 @@
           <t>令和9年度</t>
         </is>
       </c>
-      <c r="E88" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="19" t="n">
-        <v>0</v>
+      <c r="E88" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F88" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G88" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H88" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I88" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J88" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K88" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -18282,29 +18166,40 @@
           <t>令和10年度</t>
         </is>
       </c>
-      <c r="E89" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="19" t="n">
-        <v>0</v>
+      <c r="E89" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F89" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G89" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H89" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I89" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J89" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K89" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -18316,29 +18211,40 @@
           <t>令和11年度</t>
         </is>
       </c>
-      <c r="E90" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="19" t="n">
-        <v>0</v>
+      <c r="E90" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F90" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G90" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H90" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I90" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J90" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K90" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -18350,29 +18256,40 @@
           <t>令和12年度</t>
         </is>
       </c>
-      <c r="E91" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="19" t="n">
-        <v>0</v>
+      <c r="E91" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F91" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G91" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H91" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I91" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J91" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K91" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -18384,29 +18301,40 @@
           <t>令和17年度</t>
         </is>
       </c>
-      <c r="E92" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="19" t="n">
-        <v>0</v>
+      <c r="E92" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F92" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G92" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H92" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I92" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J92" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K92" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -18418,29 +18346,40 @@
           <t>令和22年度</t>
         </is>
       </c>
-      <c r="E93" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="19" t="n">
-        <v>0</v>
+      <c r="E93" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F93" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G93" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H93" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I93" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J93" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K93" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -18452,29 +18391,40 @@
           <t>令和27年度</t>
         </is>
       </c>
-      <c r="E94" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="19" t="n">
-        <v>0</v>
+      <c r="E94" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F94" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G94" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H94" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I94" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J94" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K94" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -18486,29 +18436,40 @@
           <t>令和32年度</t>
         </is>
       </c>
-      <c r="E95" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="19" t="n">
-        <v>0</v>
+      <c r="E95" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F95" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G95" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H95" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I95" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J95" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K95" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -18531,29 +18492,40 @@
 （実績）</t>
         </is>
       </c>
-      <c r="E96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="18" t="n">
-        <v>0</v>
+      <c r="E96" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F96" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G96" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H96" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I96" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J96" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K96" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -18565,29 +18537,40 @@
           <t>令和9年度</t>
         </is>
       </c>
-      <c r="E97" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="19" t="n">
-        <v>0</v>
+      <c r="E97" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F97" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G97" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H97" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I97" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J97" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K97" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -18599,29 +18582,40 @@
           <t>令和10年度</t>
         </is>
       </c>
-      <c r="E98" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="19" t="n">
-        <v>0</v>
+      <c r="E98" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F98" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G98" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H98" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I98" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J98" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K98" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -18633,29 +18627,40 @@
           <t>令和11年度</t>
         </is>
       </c>
-      <c r="E99" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="19" t="n">
-        <v>0</v>
+      <c r="E99" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F99" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G99" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H99" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I99" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J99" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K99" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -18667,29 +18672,40 @@
           <t>令和12年度</t>
         </is>
       </c>
-      <c r="E100" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="19" t="n">
-        <v>0</v>
+      <c r="E100" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F100" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G100" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H100" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I100" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J100" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K100" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -18701,29 +18717,40 @@
           <t>令和17年度</t>
         </is>
       </c>
-      <c r="E101" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="19" t="n">
-        <v>0</v>
+      <c r="E101" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F101" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G101" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H101" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I101" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J101" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K101" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -18735,29 +18762,40 @@
           <t>令和22年度</t>
         </is>
       </c>
-      <c r="E102" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="19" t="n">
-        <v>0</v>
+      <c r="E102" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F102" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G102" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H102" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I102" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J102" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K102" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -18769,29 +18807,40 @@
           <t>令和27年度</t>
         </is>
       </c>
-      <c r="E103" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="19" t="n">
-        <v>0</v>
+      <c r="E103" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F103" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G103" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H103" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I103" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J103" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K103" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -18803,29 +18852,40 @@
           <t>令和32年度</t>
         </is>
       </c>
-      <c r="E104" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="19" t="n">
-        <v>0</v>
+      <c r="E104" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F104" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G104" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H104" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I104" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J104" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K104" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -18848,29 +18908,38 @@
 （実績）</t>
         </is>
       </c>
-      <c r="E105" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="18" t="n">
-        <v>0</v>
+      <c r="E105" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F105" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G105" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="H105" s="18" t="n">
         <v>7.9</v>
       </c>
-      <c r="I105" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="18" t="n">
-        <v>7.9</v>
+      <c r="I105" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J105" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K105" s="18" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -18882,29 +18951,38 @@
           <t>令和9年度</t>
         </is>
       </c>
-      <c r="E106" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" s="19" t="n">
-        <v>0</v>
+      <c r="E106" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F106" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G106" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="H106" s="19" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="I106" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="19" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
+      </c>
+      <c r="I106" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J106" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K106" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -18916,29 +18994,38 @@
           <t>令和10年度</t>
         </is>
       </c>
-      <c r="E107" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" s="19" t="n">
-        <v>0</v>
+      <c r="E107" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F107" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G107" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="H107" s="19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I107" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="19" t="n">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
+      </c>
+      <c r="I107" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J107" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K107" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -18950,29 +19037,38 @@
           <t>令和11年度</t>
         </is>
       </c>
-      <c r="E108" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" s="19" t="n">
-        <v>0</v>
+      <c r="E108" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F108" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G108" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="H108" s="19" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I108" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="19" t="n">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
+      </c>
+      <c r="I108" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J108" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K108" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -18984,29 +19080,38 @@
           <t>令和12年度</t>
         </is>
       </c>
-      <c r="E109" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" s="19" t="n">
-        <v>0</v>
+      <c r="E109" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F109" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G109" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="H109" s="19" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I109" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="19" t="n">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
+      </c>
+      <c r="I109" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J109" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K109" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -19018,29 +19123,38 @@
           <t>令和17年度</t>
         </is>
       </c>
-      <c r="E110" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" s="19" t="n">
-        <v>0</v>
+      <c r="E110" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F110" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G110" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="H110" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="I110" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K110" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="19" t="n">
-        <v>9</v>
+        <v>7.9</v>
+      </c>
+      <c r="I110" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J110" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K110" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -19052,29 +19166,38 @@
           <t>令和22年度</t>
         </is>
       </c>
-      <c r="E111" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" s="19" t="n">
-        <v>0</v>
+      <c r="E111" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F111" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G111" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="H111" s="19" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="I111" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K111" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="19" t="n">
-        <v>9.300000000000001</v>
+        <v>7.9</v>
+      </c>
+      <c r="I111" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J111" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K111" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -19086,29 +19209,38 @@
           <t>令和27年度</t>
         </is>
       </c>
-      <c r="E112" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F112" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" s="19" t="n">
-        <v>0</v>
+      <c r="E112" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F112" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G112" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="H112" s="19" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="I112" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="19" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
+      </c>
+      <c r="I112" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J112" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K112" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -19120,47 +19252,57 @@
           <t>令和32年度</t>
         </is>
       </c>
-      <c r="E113" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" s="19" t="n">
-        <v>0</v>
+      <c r="E113" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F113" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G113" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="H113" s="19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="I113" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-    </row>
-    <row r="114" ht="90" customHeight="1">
+        <v>7.9</v>
+      </c>
+      <c r="I113" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J113" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="K113" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="104" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
           <t>注1）本表の値は必要資料が未受領であることによる暫定値です。確定値ではありません。
-注2）1人1月あたり回（日）数は要支援の群・要介護の群ごとに令和7年度の値で固定しています。年報から求めた1人1月あたり回（日）数は見える化の総括表詳細（３）と小数第4位まで一致します。
-注3）通所介護・地域密着型通所介護・通所リハビリテーション・認知症対応型通所介護の単位は「回」です（年報様式1の7も総括表詳細（３）も「回」）。短期入所の2種別は「日」です。
-注4）月包括報酬によるもの（小規模多機能型居宅介護・認知症対応型共同生活介護など）と支給決定によるもの（特定福祉用具販売・住宅改修）は回（日）数の計上がないため本表にありません。</t>
+注2）1人1月あたり回（日）数を令和7年度で固定しているため、令和9年度以降は令和7年度と同じ値になります。利用者数の側が動くことにより延べの回（日）数は年度ごとに変わります。
+注3）年報（令和7年度）の要介護度別の利用回（日）数を同じ区分の受給者数で除して求めた値です。要支援・要介護の群でまとめた値は見える化の総括表詳細（３）と小数第4位まで一致します。
+注4）通所介護・地域密着型通所介護・通所リハビリテーション・認知症対応型通所介護の単位は「回」です（年報様式1の7も総括表詳細（３）も「回」）。短期入所の2種別は「日」です。
+注5）月包括報酬によるもの（小規模多機能型居宅介護・認知症対応型共同生活介護など）と支給決定によるもの（特定福祉用具販売・住宅改修）は回（日）数の計上がないため画面のプルダウンにも本表にもありません。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A114:L114"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A114:K114"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>

--- a/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
+++ b/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
@@ -814,22 +814,22 @@
       <c r="C12" s="9" t="inlineStr"/>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>2,978,267,893</t>
+          <t>2,978,975,041</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>3,010,470,894</t>
+          <t>3,011,540,164</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>3,043,161,657</t>
+          <t>3,044,598,937</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>3か年計 9,031,900,444円。09シート</t>
+          <t>3か年計 9,035,114,142円。09シート</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr"/>
@@ -1270,22 +1270,22 @@
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>2,978,267,893</t>
+          <t>2,978,975,041</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>3,010,470,894</t>
+          <t>3,011,540,164</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>3,043,161,657</t>
+          <t>3,044,598,937</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>9,031,900,444</t>
+          <t>9,035,114,142</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       <c r="E7" s="9" t="inlineStr"/>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>6,436円</t>
+          <t>6,438円</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>+566円</t>
+          <t>+564円</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>-257円</t>
+          <t>-259円</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>6,436円</t>
+          <t>6,438円</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -1584,17 +1584,17 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>ツールから要介護度間の比（形）だけを採り、水準は総括表に合わせて比例調整した。採用値は単価固定（06シート）のままとし、07シートに別掲した</t>
+          <t>令和8年10月1日に採用し、据え置きを解消した。要介護度間の比を給付費データ（保険者単位）から採り、水準は総括表に合わせて比例調整している。基準年度では総括表の給付費を円単位で再現する（点検16）</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>要介護度別の単価を用いると令和11年度＋0.047％（月額＋2円）、令和22年度＋0.280％</t>
+          <t>採用により総給付費（3か年）＋3,213,698円・月額＋2.17円。保険料基準額は6,400円で変わらない</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -1614,17 +1614,17 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の実績で固定した</t>
+          <t>令和8年10月1日に要介護度別に改め、据え置きを解消した。従前は要支援・要介護の群でまとめた1人1月あたりで置いていた</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>回数のみでは月額への効きは小さい</t>
+          <t>給付費には入らないため月額への効きはない。延べの回（日）数が最大＋0.09％（訪問介護）動く</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>一律の伸びとの差は月額+8円</t>
+          <t>一律の伸びとの差は月額+10円</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>季節指数の和が12となり換算係数が1.0000で恒等的に消える。補正を行わない</t>
+          <t>季節指数の和が12となり換算係数が1.0000で恒等的に消える。補正を行わない。基準年度を完結年度に採る限り効きは0円であり、測定できても採用値は動かない</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -2233,10 +2233,11 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="76" customHeight="1">
+    <row r="29" ht="86" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>注1）区分A（4件）は受託者の側で確定できるもので、資料を要しません。
+          <t>注0）解消済み（2件）は令和8年10月1日に当方で確定したものです（要介護度別の単価・要介護度別の1人1月あたり利用回（日）数）。
+注1）区分A（2件）は受託者の側で確定できるもので、資料を要しません。
 注2）区分B（15件）は発注者・3町の資料待ちですが、届かなければ据え置きのまま確定します。算定は止まりません。
 注3）区分C（4件）は国の告示・公布を待つもので、「受領できない」では済みません。報酬改定率・第1号被保険者負担割合・所得段階の政令改正・令和9年4月新設の3区分です。
 注4）発注者・3町から追加の資料がまったく届かなくても、国の告示さえ出れば計画は確定します。</t>
@@ -2861,12 +2862,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>据え置きの区分がA・B・Cに漏れなく分かれていること</t>
+          <t>据え置きの区分が解消済み・A・B・Cに漏れなく分かれていること</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>A4＋B15＋C4</t>
+          <t>Z2＋A2＋B15＋C4</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -2891,7 +2892,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>round(6436/100)*100</t>
+          <t>round(6438/100)*100</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -3425,12 +3426,12 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたりに改めた（画面の写しによる。値の性質が変わったもので、延べに戻せば9月18日版と同じ）</t>
+          <t>1人1月あたりに改めた（画面の写しによる）。令和8年10月1日に要介護度別の1人1月あたりに改めたため、延べに戻しても9月18日版と完全には一致しない（最大＋0.09％）</t>
         </is>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>掲げ方を改めた</t>
+          <t>掲げ方と置き方を改めた</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3460,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="44" customHeight="1">
       <c r="A11" s="15" t="n">
         <v>6</v>
       </c>
@@ -3475,16 +3476,16 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>9,031,900,444円</t>
-        </is>
-      </c>
-      <c r="E11" s="34" t="inlineStr">
-        <is>
-          <t>変わらない</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
+          <t>9,035,114,142円（令和8年10月1日に要介護度別の単価を採用したことによる。＋0.036％）</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>動いた</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
       <c r="A12" s="15" t="n">
         <v>7</v>
       </c>
@@ -3500,12 +3501,12 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>6,436円</t>
-        </is>
-      </c>
-      <c r="E12" s="34" t="inlineStr">
-        <is>
-          <t>変わらない</t>
+          <t>6,438円（同上。＋2.17円）</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>動いた</t>
         </is>
       </c>
     </row>
@@ -21803,7 +21804,7 @@
       <c r="A43" s="2" t="inlineStr">
         <is>
           <t>注1）本表の値は必要資料が未受領であることによる暫定値です。確定値ではありません。
-注2）画面に表示されている割合は国の標準（13段階）であり、当連合の条例の乗率とは異なります。第2・第4・第6から第9・第11から第13段階の9つで違いがあり、第14から第16段階（多段階化した分）は標準にありません。本表の人数を標準の割合のまま入れると、第10期3か年の補正後被保険者数は27,090.8人（条例の乗率なら27,298.8人）となり、算定上の月額は6436円から6485円へ+49円動きます。
+注2）画面に表示されている割合は国の標準（13段階）であり、当連合の条例の乗率とは異なります。第2・第4・第6から第9・第11から第13段階の9つで違いがあり、第14から第16段階（多段階化した分）は標準にありません。本表の人数を標準の割合のまま入れると、第10期3か年の補正後被保険者数は27,090.8人（条例の乗率なら27,298.8人）となり、算定上の月額は6438円から6487円へ+49円動きます。
 注3）したがって、所得段階の設定は「弾力化」を選び、1の表（16段階）の人数と乗率を入れることを基本とします。標準の13段階のまま入れるのは、画面が弾力化を受け付けない場合に限ります。
 注4）画面が表示する第1号被保険者数は人口の設定によります。人口の設定が社人研のままのとき、画面は令和9年度9,116人・令和10年度9,110人・令和11年度9,107人を表示します。本表の計（9,147人・9,179人・9,213人）は案Cによるものであり、先に人口の設定を案Cに改めないと計が画面と合いません（確認事項No.127）。</t>
         </is>

--- a/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
+++ b/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
@@ -1639,22 +1639,22 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>要介護度の構成　要介護度別の将来推計</t>
+          <t>要介護度の構成　―</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定した。年齢構成の変化による重度化は反映される</t>
+          <t>令和8年10月1日に確定した。年齢階級ごとの要介護度の構成を令和7年度末（年報 様式1の5）の実績で固定し、将来推計 第1段階の年齢階級別認定者数に乗じる。年齢構成の変化による重度化は反映され、要介護度別の和は第1段階の認定者数と完全に一致する（点検3・点検11）</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>一律の伸びとの差は月額+10円</t>
+          <t>一律の伸びとの差は月額＋10円</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>季節指数の和が12となり換算係数が1.0000で恒等的に消える。補正を行わない。基準年度を完結年度に採る限り効きは0円であり、測定できても採用値は動かない</t>
+          <t>令和8年10月1日に確定した。季節補正を行わない。基準年度が12か月の完結年度であるため季節指数の和は12となり、年度換算係数は12÷12＝1.0000で恒等的に消える。季節性を測定できるようになっても採用値は動かないため、資料の受領を待たない</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -2236,8 +2236,8 @@
     <row r="29" ht="86" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>注0）解消済み（2件）は令和8年10月1日に当方で確定したものです（要介護度別の単価・要介護度別の1人1月あたり利用回（日）数）。
-注1）区分A（2件）は受託者の側で確定できるもので、資料を要しません。
+          <t>注0）解消済み（4件）は令和8年10月1日に当方で確定したものです（要介護度別の単価・要介護度別の1人1月あたり利用回（日）数）。
+注1）区分A（0件）は受託者の側で確定できるもので、資料を要しません。
 注2）区分B（15件）は発注者・3町の資料待ちですが、届かなければ据え置きのまま確定します。算定は止まりません。
 注3）区分C（4件）は国の告示・公布を待つもので、「受領できない」では済みません。報酬改定率・第1号被保険者負担割合・所得段階の政令改正・令和9年4月新設の3区分です。
 注4）発注者・3町から追加の資料がまったく届かなくても、国の告示さえ出れば計画は確定します。</t>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Z2＋A2＋B15＋C4</t>
+          <t>Z4＋A0＋B15＋C4</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">

--- a/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
+++ b/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
@@ -1334,7 +1334,7 @@
         <is>
           <t>注1）本表の値は必要資料が未受領であることによる暫定値です。確定値ではありません。
 注2）保険料基準額6,400円は第9期と同額です（第9期は算定上6,428円→基準額6,400円）。
-注3）この値は据え置き前提の下限に近いものです。単価を令和7年度で固定し、年率1.75％の伸びを見込んでいません（織り込むと月額＋185円から＋374円）。介護報酬改定率3％で＋182円、第1号被保険者負担割合1ポイントで約＋290円です。いずれも国の告示・公布によるもので、資料の受領とは関係なく生じます。</t>
+注3）この値は据え置き前提の下限に近いものです。単価を令和7年度で固定し、年率1.32％から1.75％の伸びを見込んでいません（織り込むと月額＋245円から＋327円）。介護報酬改定率3％で＋182円、第1号被保険者負担割合1ポイントで約＋290円です。いずれも国の告示・公布によるもので、資料の受領とは関係なく生じます。</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>改定率1％あたり月額＋61円。単価の年率1.75％の伸びを見込まないことは月額＋185〜＋374円に当たる</t>
+          <t>改定率1％あたり月額＋61円。単価の年率1.75％の伸びを見込まないことは月額＋245円〜＋327円に当たる</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>年度の選択は＋185〜＋374円</t>
+          <t>年度の選択は＋245円〜＋327円</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -4410,7 +4410,7 @@
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>注1）令和8年度の実績見込み値に入れる数値は別冊「見える化 令和8年度実績見込み値の入力案」（15シート）に掲げています。本表は令和9年度以降の見込量です。
-注2）1人1月あたり給付費の実績値をどの年度（令和7年度か令和8年度か）にするかを選ぶ項目があります（施設・居住系と在宅で別に選べます）。当方は令和7年度で固定しており、これは月額で＋185円から＋374円に当たります。ご判断を要します（確認事項No.137）。
+注2）1人1月あたり給付費の実績値をどの年度（令和7年度か令和8年度か）にするかを選ぶ項目があります（施設・居住系と在宅で別に選べます）。当方は令和7年度で固定しており、これは月額で＋245円から＋327円に当たります。ご判断を要します（確認事項No.137）。
 注3）認定者数の実績見込み値を編集する項目が画面にあるかを確かめられていません（確認事項No.138）。編集項目がない場合は、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶことで令和8年度の影響を避けます。</t>
         </is>
       </c>

--- a/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
+++ b/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
@@ -1564,7 +1564,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>改定率1％あたり月額＋61円。単価の年率1.75％の伸びを見込まないことは月額＋245円〜＋327円に当たる</t>
+          <t>改定率1％あたり月額＋61円。単価の年率1.32％から1.75％の伸びを見込まないことは月額＋245円〜＋327円に当たり、令和8年度の水準（残差＋1.63％）に置くと月額＋99円（確認事項No.104）</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">

--- a/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
+++ b/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>採用により総給付費（3か年）＋3,213,698円・月額＋2.17円。保険料基準額は6,400円で変わらない</t>
+          <t>採用により総給付費（3か年）＋3,213,698円・月額＋2.16円。保険料基準額は6,400円で変わらない</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">

--- a/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
+++ b/output/第10期計画_見える化_見込量の入力値（暫定）.xlsx
@@ -21113,7 +21113,7 @@
           <t>注1）本表の値は必要資料が未受領であることによる暫定値です。確定値ではありません。
 注2）割合は公費軽減前の値です。第1段階から第3段階は公費軽減の対象ですが、補正後被保険者数はこの割合で算定します（公費軽減分は国・都道府県・市町村の公費で補填されます）。見える化システムが「①標準段階区分・割合」の画面に表示する0.4550・0.6850・0.6900…も公費軽減前の値であり、基準がそろっています。保険料収入と低所得者軽減公費を別々に置く様式では、この割合で計算した収入に軽減公費を重ねて加えないでください。
 注3）基準所得金額は第7段階から第16段階の10件です。第1段階から第6段階は本人の合計所得金額の下限による区分ではないため（生活保護受給・世帯の課税状況・合計所得金額＋課税年金収入額による）基準所得金額を持ちません。画面も当該欄は入力を受け付けません。第7段階から第13段階の額は、画面が標準として表示している1,200,000円から7,200,000円と一致します。
-注4）構成比は令和6年度の実績で固定しています。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数からシステムが算定する補正後被保険者数は当方の値と一致します。令和7年度の構成比に改めると係数は1.015890となり、算定上の月額が163円下がります。これは構成比の作り方ではなく係数の選択そのものです。
+注4）構成比は令和6年度の実績で固定しています。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数からシステムが算定する補正後被保険者数は当方の値と一致します。令和7年度の構成比に改めると係数は1.015890となり、算定上の月額が▲156円動きます。これは構成比の作り方ではなく係数の選択そのものです。
 注5）第10期の段階数・割合・基準所得金額は政令改正により変わり得ます（確認事項No.33）。本表は第9期の条例の16段階・割合による暫定の値です。令和8年3月の全国課長会議資料は、保険料段階の基準額を80.9万円から82.65万円に改める政令改正が済んでおり、条例改正の手続を要するとしています。</t>
         </is>
       </c>
